--- a/Mapping & Audit Data/Objects Mapping Sheet.xlsx
+++ b/Mapping & Audit Data/Objects Mapping Sheet.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="108">
   <si>
     <t>Object Type</t>
   </si>
@@ -70,20 +70,7 @@
     <t>Standard</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t>User | Group | Account | Contact | RecordType |</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FFFF0000"/>
-      </rPr>
-      <t xml:space="preserve"> Individual | Maps Assignment Rule(maps__AssignmentRule__c)</t>
-    </r>
+    <t xml:space="preserve">User | Group | Account | Contact | RecordType </t>
   </si>
   <si>
     <t>OwnerId | RecordTypeId | PartnerAccountId | IndividualId | Co_Owner__c | Transfer_User__c | National_Account__c | maps__AssignmentRule__c</t>
@@ -95,55 +82,7 @@
     <t>Opportunity</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">Account | RecordType | Campaign | Pricebook2 | User | </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FFFF0000"/>
-      </rPr>
-      <t xml:space="preserve">Territory2 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">| Contact | </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FFFF0000"/>
-      </rPr>
-      <t xml:space="preserve">Quote </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">| </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FFFF0000"/>
-      </rPr>
-      <t xml:space="preserve">Contract </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t>| Location | Product2 | Opportunity</t>
-    </r>
+    <t>Account | RecordType | Campaign | Pricebook2 | User | Contact | Location | Product2 | Opportunity</t>
   </si>
   <si>
     <t>AccountId | RecordTypeId | CampaignId | Pricebook2Id | OwnerId | Territory2Id | ContactId | PartnerAccountId | SyncedQuoteId | ContractId | Builder_Contact__c | Primary_Dealer__c | Architect_Contact__c | Builder__c | Outside_Rep_1__c | Outside_Rep_2__c | Inside_Rep_1__c | Inside_Rep_2__c | Arch_Rep__c | Architect__c | Dealer_Contact__c | Opportunities_Manual_Entry__c | Opportunities_CV__c | Arch_Opp_ClosedWon__c | Job_Location__c | Product__c | FSSR__c | Co_Owner__c | Parent_Opportunity__c</t>
@@ -155,22 +94,7 @@
     <t>Campaign</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve">User | ContentDocument | PardotTenant | RecordType | Campaign | </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b val="0"/>
-        <color rgb="FFFF0000"/>
-      </rPr>
-      <t>'Business Unit'(compliancequest__SQX_Business_Unit__c)</t>
-    </r>
+    <t xml:space="preserve">User | ContentDocument | PardotTenant | RecordType | Campaign </t>
   </si>
   <si>
     <t>OwnerId | CampaignImageId | TenantId | CampaignMemberRecordTypeId | ParentId</t>
@@ -348,6 +272,69 @@
   </si>
   <si>
     <t>Account__c | Name_of_dealer_visited__c | OwnerId | Performance_Card__c</t>
+  </si>
+  <si>
+    <t>Marketing Development Allocation</t>
+  </si>
+  <si>
+    <t>Marketing_Development_Allocation__c</t>
+  </si>
+  <si>
+    <t>User | Group | Marketing_Development_Budget__c</t>
+  </si>
+  <si>
+    <t>OwnerId | Budget__c</t>
+  </si>
+  <si>
+    <t>Marketing Development Budget</t>
+  </si>
+  <si>
+    <t>Marketing_Development_Budget__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User | Group </t>
+  </si>
+  <si>
+    <t>OwnerId</t>
+  </si>
+  <si>
+    <t>Marketing Development Claim</t>
+  </si>
+  <si>
+    <t>Marketing_Development_Claim__c</t>
+  </si>
+  <si>
+    <t>Marketing_Development_Fund__c | Marketing_Development_Allocation__c</t>
+  </si>
+  <si>
+    <t>Marketing Development Fund</t>
+  </si>
+  <si>
+    <t>Marketing_Development_Fund__c</t>
+  </si>
+  <si>
+    <t>User | Group | Marketing_Development_Allocation__c | Contact | Account</t>
+  </si>
+  <si>
+    <t>OwnerId | Marketing_Development_Allocation__c | Marketing_Contact__c | Account__c</t>
+  </si>
+  <si>
+    <t>Marketing Development Request</t>
+  </si>
+  <si>
+    <t>Marketing_Development_Request__c</t>
+  </si>
+  <si>
+    <t>Marketing_Development_Allocation__c | Marketing_Development_Fund__c</t>
+  </si>
+  <si>
+    <t>Related Account</t>
+  </si>
+  <si>
+    <t>Related_Account__c</t>
+  </si>
+  <si>
+    <t>OwnerId | Related_Account__c | Primary_Account__c</t>
   </si>
 </sst>
 </file>
@@ -357,7 +344,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm-dd-yyyy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -413,6 +400,10 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color rgb="FF181818"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -439,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -460,7 +451,10 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -475,10 +469,10 @@
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -503,14 +497,20 @@
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -731,7 +731,8 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="11.63"/>
     <col customWidth="1" min="2" max="2" width="20.75"/>
-    <col customWidth="1" min="3" max="4" width="24.63"/>
+    <col customWidth="1" min="3" max="3" width="31.0"/>
+    <col customWidth="1" min="4" max="4" width="24.63"/>
     <col customWidth="1" min="5" max="5" width="22.5"/>
     <col customWidth="1" min="6" max="6" width="31.5"/>
     <col customWidth="1" min="7" max="7" width="18.63"/>
@@ -823,12 +824,12 @@
         <v>59002.0</v>
       </c>
       <c r="F2" s="9">
-        <v>46238.0</v>
+        <v>46120.0</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>20</v>
       </c>
       <c r="I2" s="6" t="s">
@@ -843,10 +844,10 @@
       <c r="L2" s="8">
         <v>430730.0</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="13" t="s">
         <v>17</v>
       </c>
     </row>
@@ -867,12 +868,12 @@
         <v>447273.0</v>
       </c>
       <c r="F3" s="9">
-        <v>46238.0</v>
+        <v>46120.0</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>24</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -887,13 +888,13 @@
       <c r="L3" s="8">
         <v>42502.0</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -914,12 +915,12 @@
         <v>31.0</v>
       </c>
       <c r="F4" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G4" s="14" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="16" t="s">
         <v>28</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -934,10 +935,10 @@
       <c r="L4" s="8">
         <v>295.0</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -958,12 +959,12 @@
         <v>12950.0</v>
       </c>
       <c r="F5" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G5" s="10" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -978,10 +979,10 @@
       <c r="L5" s="8">
         <v>1919.0</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="O5" s="13" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1002,12 +1003,12 @@
         <v>62.0</v>
       </c>
       <c r="F6" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G6" s="10" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="6" t="s">
@@ -1022,10 +1023,10 @@
       <c r="L6" s="8">
         <v>591.0</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="12" t="s">
+      <c r="O6" s="13" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1046,12 +1047,12 @@
         <v>4823470.0</v>
       </c>
       <c r="F7" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G7" s="15" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="10" t="s">
         <v>40</v>
       </c>
       <c r="I7" s="6" t="s">
@@ -1066,10 +1067,10 @@
       <c r="L7" s="8">
         <v>0.0</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="O7" s="13" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1090,12 +1091,12 @@
         <v>70550.0</v>
       </c>
       <c r="F8" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G8" s="15" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="10" t="s">
         <v>40</v>
       </c>
       <c r="I8" s="6" t="s">
@@ -1110,10 +1111,10 @@
       <c r="L8" s="8">
         <v>0.0</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O8" s="12" t="s">
+      <c r="O8" s="13" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1134,12 +1135,12 @@
         <v>4409252.0</v>
       </c>
       <c r="F9" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G9" s="15" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="10" t="s">
         <v>47</v>
       </c>
       <c r="I9" s="6" t="s">
@@ -1154,10 +1155,10 @@
       <c r="L9" s="8">
         <v>1.8029724E7</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O9" s="12" t="s">
+      <c r="O9" s="13" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1178,12 +1179,12 @@
         <v>21917.0</v>
       </c>
       <c r="F10" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G10" s="10" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>51</v>
       </c>
       <c r="I10" s="6" t="s">
@@ -1198,10 +1199,10 @@
       <c r="L10" s="8">
         <v>375.0</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="13" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1222,12 +1223,12 @@
         <v>492503.0</v>
       </c>
       <c r="F11" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G11" s="10" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>55</v>
       </c>
       <c r="I11" s="6" t="s">
@@ -1242,10 +1243,10 @@
       <c r="L11" s="8">
         <v>1093.0</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O11" s="12" t="s">
+      <c r="O11" s="13" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1266,17 +1267,17 @@
         <v>844.0</v>
       </c>
       <c r="F12" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G12" s="10" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="12" t="s">
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="13" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1297,15 +1298,15 @@
         <v>13.0</v>
       </c>
       <c r="F13" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G13" s="10" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G13" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="O13" s="12" t="s">
+      <c r="O13" s="13" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1326,15 +1327,15 @@
         <v>102542.0</v>
       </c>
       <c r="F14" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G14" s="10" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="O14" s="13" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1355,15 +1356,15 @@
         <v>7335.0</v>
       </c>
       <c r="F15" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G15" s="10" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G15" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="O15" s="12" t="s">
+      <c r="O15" s="13" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1371,10 +1372,10 @@
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="18" t="s">
         <v>73</v>
       </c>
       <c r="D16" s="7" t="s">
@@ -1384,15 +1385,15 @@
         <v>64303.0</v>
       </c>
       <c r="F16" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G16" s="18" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G16" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="O16" s="12" t="s">
+      <c r="O16" s="13" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1413,15 +1414,15 @@
         <v>5236.0</v>
       </c>
       <c r="F17" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G17" s="20" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G17" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="H17" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="O17" s="12" t="s">
+      <c r="O17" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1429,7 +1430,7 @@
       <c r="A18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="23" t="s">
         <v>79</v>
       </c>
       <c r="C18" s="6" t="s">
@@ -1442,15 +1443,15 @@
         <v>5451.0</v>
       </c>
       <c r="F18" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G18" s="20" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G18" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="21" t="s">
+      <c r="H18" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="O18" s="12" t="s">
+      <c r="O18" s="13" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1458,10 +1459,10 @@
       <c r="A19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="24" t="s">
         <v>84</v>
       </c>
       <c r="D19" s="7" t="s">
@@ -1471,2963 +1472,3091 @@
         <v>47964.0</v>
       </c>
       <c r="F19" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="G19" s="24" t="s">
+        <v>46120.0</v>
+      </c>
+      <c r="G19" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="24" t="s">
+      <c r="H19" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="O19" s="12" t="s">
+      <c r="O19" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="20">
-      <c r="D20" s="5"/>
-      <c r="G20" s="25"/>
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="24">
+        <v>31.0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>46121.0</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="26" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="21">
-      <c r="D21" s="5"/>
-      <c r="G21" s="25"/>
+      <c r="A21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="24">
+        <v>4.0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>46121.0</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="22">
-      <c r="D22" s="5"/>
-      <c r="G22" s="25"/>
+      <c r="A22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="24">
+        <v>1169.0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>46121.0</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="23">
-      <c r="D23" s="5"/>
-      <c r="G23" s="25"/>
+      <c r="A23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="24">
+        <v>1629.0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>46121.0</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="H23" s="25" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="24">
-      <c r="D24" s="5"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="26"/>
+      <c r="A24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="24">
+        <v>1095.0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>46121.0</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="25">
-      <c r="D25" s="5"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="26"/>
+      <c r="A25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="24">
+        <v>1707.0</v>
+      </c>
+      <c r="F25" s="9">
+        <v>46121.0</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" s="27" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="26">
       <c r="D26" s="5"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="26"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="28"/>
     </row>
     <row r="27">
       <c r="D27" s="5"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="26"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="28"/>
     </row>
     <row r="28">
       <c r="D28" s="5"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="26"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="28"/>
     </row>
     <row r="29">
       <c r="D29" s="5"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="26"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="28"/>
     </row>
     <row r="30">
       <c r="D30" s="5"/>
-      <c r="G30" s="25"/>
+      <c r="G30" s="30"/>
     </row>
     <row r="31">
-      <c r="G31" s="25"/>
+      <c r="G31" s="30"/>
     </row>
     <row r="32">
-      <c r="G32" s="25"/>
+      <c r="G32" s="30"/>
     </row>
     <row r="33">
-      <c r="G33" s="25"/>
+      <c r="G33" s="30"/>
     </row>
     <row r="34">
-      <c r="G34" s="25"/>
+      <c r="G34" s="30"/>
     </row>
     <row r="35">
-      <c r="G35" s="25"/>
+      <c r="G35" s="30"/>
     </row>
     <row r="36">
-      <c r="G36" s="25"/>
+      <c r="G36" s="30"/>
     </row>
     <row r="37">
-      <c r="G37" s="25"/>
+      <c r="G37" s="30"/>
     </row>
     <row r="38">
-      <c r="G38" s="25"/>
+      <c r="G38" s="30"/>
     </row>
     <row r="39">
-      <c r="G39" s="25"/>
+      <c r="G39" s="30"/>
     </row>
     <row r="40">
-      <c r="G40" s="25"/>
+      <c r="G40" s="30"/>
     </row>
     <row r="41">
-      <c r="G41" s="25"/>
+      <c r="G41" s="30"/>
     </row>
     <row r="42">
-      <c r="G42" s="25"/>
+      <c r="G42" s="30"/>
     </row>
     <row r="43">
-      <c r="G43" s="25"/>
+      <c r="G43" s="30"/>
     </row>
     <row r="44">
-      <c r="G44" s="25"/>
+      <c r="G44" s="30"/>
     </row>
     <row r="45">
-      <c r="G45" s="25"/>
+      <c r="G45" s="30"/>
     </row>
     <row r="46">
-      <c r="G46" s="25"/>
+      <c r="G46" s="30"/>
     </row>
     <row r="47">
-      <c r="G47" s="25"/>
+      <c r="G47" s="30"/>
     </row>
     <row r="48">
-      <c r="G48" s="25"/>
+      <c r="G48" s="30"/>
     </row>
     <row r="49">
-      <c r="G49" s="25"/>
+      <c r="G49" s="30"/>
     </row>
     <row r="50">
-      <c r="G50" s="25"/>
+      <c r="G50" s="30"/>
     </row>
     <row r="51">
-      <c r="G51" s="25"/>
+      <c r="G51" s="30"/>
     </row>
     <row r="52">
-      <c r="G52" s="25"/>
+      <c r="G52" s="30"/>
     </row>
     <row r="53">
-      <c r="G53" s="25"/>
+      <c r="G53" s="30"/>
     </row>
     <row r="54">
-      <c r="G54" s="25"/>
+      <c r="G54" s="30"/>
     </row>
     <row r="55">
-      <c r="G55" s="25"/>
+      <c r="G55" s="30"/>
     </row>
     <row r="56">
-      <c r="G56" s="25"/>
+      <c r="G56" s="30"/>
     </row>
     <row r="57">
-      <c r="G57" s="25"/>
+      <c r="G57" s="30"/>
     </row>
     <row r="58">
-      <c r="G58" s="25"/>
+      <c r="G58" s="30"/>
     </row>
     <row r="59">
-      <c r="G59" s="25"/>
+      <c r="G59" s="30"/>
     </row>
     <row r="60">
-      <c r="G60" s="25"/>
+      <c r="G60" s="30"/>
     </row>
     <row r="61">
-      <c r="G61" s="25"/>
+      <c r="G61" s="30"/>
     </row>
     <row r="62">
-      <c r="G62" s="25"/>
+      <c r="G62" s="30"/>
     </row>
     <row r="63">
-      <c r="G63" s="25"/>
+      <c r="G63" s="30"/>
     </row>
     <row r="64">
-      <c r="G64" s="25"/>
+      <c r="G64" s="30"/>
     </row>
     <row r="65">
-      <c r="G65" s="25"/>
+      <c r="G65" s="30"/>
     </row>
     <row r="66">
-      <c r="G66" s="25"/>
+      <c r="G66" s="30"/>
     </row>
     <row r="67">
-      <c r="G67" s="25"/>
+      <c r="G67" s="30"/>
     </row>
     <row r="68">
-      <c r="G68" s="25"/>
+      <c r="G68" s="30"/>
     </row>
     <row r="69">
-      <c r="G69" s="25"/>
+      <c r="G69" s="30"/>
     </row>
     <row r="70">
-      <c r="G70" s="25"/>
+      <c r="G70" s="30"/>
     </row>
     <row r="71">
-      <c r="G71" s="25"/>
+      <c r="G71" s="30"/>
     </row>
     <row r="72">
-      <c r="G72" s="25"/>
+      <c r="G72" s="30"/>
     </row>
     <row r="73">
-      <c r="G73" s="25"/>
+      <c r="G73" s="30"/>
     </row>
     <row r="74">
-      <c r="G74" s="25"/>
+      <c r="G74" s="30"/>
     </row>
     <row r="75">
-      <c r="G75" s="25"/>
+      <c r="G75" s="30"/>
     </row>
     <row r="76">
-      <c r="G76" s="25"/>
+      <c r="G76" s="30"/>
     </row>
     <row r="77">
-      <c r="G77" s="25"/>
+      <c r="G77" s="30"/>
     </row>
     <row r="78">
-      <c r="G78" s="25"/>
+      <c r="G78" s="30"/>
     </row>
     <row r="79">
-      <c r="G79" s="25"/>
+      <c r="G79" s="30"/>
     </row>
     <row r="80">
-      <c r="G80" s="25"/>
+      <c r="G80" s="30"/>
     </row>
     <row r="81">
-      <c r="G81" s="25"/>
+      <c r="G81" s="30"/>
     </row>
     <row r="82">
-      <c r="G82" s="25"/>
+      <c r="G82" s="30"/>
     </row>
     <row r="83">
-      <c r="G83" s="25"/>
+      <c r="G83" s="30"/>
     </row>
     <row r="84">
-      <c r="G84" s="25"/>
+      <c r="G84" s="30"/>
     </row>
     <row r="85">
-      <c r="G85" s="25"/>
+      <c r="G85" s="30"/>
     </row>
     <row r="86">
-      <c r="G86" s="25"/>
+      <c r="G86" s="30"/>
     </row>
     <row r="87">
-      <c r="G87" s="25"/>
+      <c r="G87" s="30"/>
     </row>
     <row r="88">
-      <c r="G88" s="25"/>
+      <c r="G88" s="30"/>
     </row>
     <row r="89">
-      <c r="G89" s="25"/>
+      <c r="G89" s="30"/>
     </row>
     <row r="90">
-      <c r="G90" s="25"/>
+      <c r="G90" s="30"/>
     </row>
     <row r="91">
-      <c r="G91" s="25"/>
+      <c r="G91" s="30"/>
     </row>
     <row r="92">
-      <c r="G92" s="25"/>
+      <c r="G92" s="30"/>
     </row>
     <row r="93">
-      <c r="G93" s="25"/>
+      <c r="G93" s="30"/>
     </row>
     <row r="94">
-      <c r="G94" s="25"/>
+      <c r="G94" s="30"/>
     </row>
     <row r="95">
-      <c r="G95" s="25"/>
+      <c r="G95" s="30"/>
     </row>
     <row r="96">
-      <c r="G96" s="25"/>
+      <c r="G96" s="30"/>
     </row>
     <row r="97">
-      <c r="G97" s="25"/>
+      <c r="G97" s="30"/>
     </row>
     <row r="98">
-      <c r="G98" s="25"/>
+      <c r="G98" s="30"/>
     </row>
     <row r="99">
-      <c r="G99" s="25"/>
+      <c r="G99" s="30"/>
     </row>
     <row r="100">
-      <c r="G100" s="25"/>
+      <c r="G100" s="30"/>
     </row>
     <row r="101">
-      <c r="G101" s="25"/>
+      <c r="G101" s="30"/>
     </row>
     <row r="102">
-      <c r="G102" s="25"/>
+      <c r="G102" s="30"/>
     </row>
     <row r="103">
-      <c r="G103" s="25"/>
+      <c r="G103" s="30"/>
     </row>
     <row r="104">
-      <c r="G104" s="25"/>
+      <c r="G104" s="30"/>
     </row>
     <row r="105">
-      <c r="G105" s="25"/>
+      <c r="G105" s="30"/>
     </row>
     <row r="106">
-      <c r="G106" s="25"/>
+      <c r="G106" s="30"/>
     </row>
     <row r="107">
-      <c r="G107" s="25"/>
+      <c r="G107" s="30"/>
     </row>
     <row r="108">
-      <c r="G108" s="25"/>
+      <c r="G108" s="30"/>
     </row>
     <row r="109">
-      <c r="G109" s="25"/>
+      <c r="G109" s="30"/>
     </row>
     <row r="110">
-      <c r="G110" s="25"/>
+      <c r="G110" s="30"/>
     </row>
     <row r="111">
-      <c r="G111" s="25"/>
+      <c r="G111" s="30"/>
     </row>
     <row r="112">
-      <c r="G112" s="25"/>
+      <c r="G112" s="30"/>
     </row>
     <row r="113">
-      <c r="G113" s="25"/>
+      <c r="G113" s="30"/>
     </row>
     <row r="114">
-      <c r="G114" s="25"/>
+      <c r="G114" s="30"/>
     </row>
     <row r="115">
-      <c r="G115" s="25"/>
+      <c r="G115" s="30"/>
     </row>
     <row r="116">
-      <c r="G116" s="25"/>
+      <c r="G116" s="30"/>
     </row>
     <row r="117">
-      <c r="G117" s="25"/>
+      <c r="G117" s="30"/>
     </row>
     <row r="118">
-      <c r="G118" s="25"/>
+      <c r="G118" s="30"/>
     </row>
     <row r="119">
-      <c r="G119" s="25"/>
+      <c r="G119" s="30"/>
     </row>
     <row r="120">
-      <c r="G120" s="25"/>
+      <c r="G120" s="30"/>
     </row>
     <row r="121">
-      <c r="G121" s="25"/>
+      <c r="G121" s="30"/>
     </row>
     <row r="122">
-      <c r="G122" s="25"/>
+      <c r="G122" s="30"/>
     </row>
     <row r="123">
-      <c r="G123" s="25"/>
+      <c r="G123" s="30"/>
     </row>
     <row r="124">
-      <c r="G124" s="25"/>
+      <c r="G124" s="30"/>
     </row>
     <row r="125">
-      <c r="G125" s="25"/>
+      <c r="G125" s="30"/>
     </row>
     <row r="126">
-      <c r="G126" s="25"/>
+      <c r="G126" s="30"/>
     </row>
     <row r="127">
-      <c r="G127" s="25"/>
+      <c r="G127" s="30"/>
     </row>
     <row r="128">
-      <c r="G128" s="25"/>
+      <c r="G128" s="30"/>
     </row>
     <row r="129">
-      <c r="G129" s="25"/>
+      <c r="G129" s="30"/>
     </row>
     <row r="130">
-      <c r="G130" s="25"/>
+      <c r="G130" s="30"/>
     </row>
     <row r="131">
-      <c r="G131" s="25"/>
+      <c r="G131" s="30"/>
     </row>
     <row r="132">
-      <c r="G132" s="25"/>
+      <c r="G132" s="30"/>
     </row>
     <row r="133">
-      <c r="G133" s="25"/>
+      <c r="G133" s="30"/>
     </row>
     <row r="134">
-      <c r="G134" s="25"/>
+      <c r="G134" s="30"/>
     </row>
     <row r="135">
-      <c r="G135" s="25"/>
+      <c r="G135" s="30"/>
     </row>
     <row r="136">
-      <c r="G136" s="25"/>
+      <c r="G136" s="30"/>
     </row>
     <row r="137">
-      <c r="G137" s="25"/>
+      <c r="G137" s="30"/>
     </row>
     <row r="138">
-      <c r="G138" s="25"/>
+      <c r="G138" s="30"/>
     </row>
     <row r="139">
-      <c r="G139" s="25"/>
+      <c r="G139" s="30"/>
     </row>
     <row r="140">
-      <c r="G140" s="25"/>
+      <c r="G140" s="30"/>
     </row>
     <row r="141">
-      <c r="G141" s="25"/>
+      <c r="G141" s="30"/>
     </row>
     <row r="142">
-      <c r="G142" s="25"/>
+      <c r="G142" s="30"/>
     </row>
     <row r="143">
-      <c r="G143" s="25"/>
+      <c r="G143" s="30"/>
     </row>
     <row r="144">
-      <c r="G144" s="25"/>
+      <c r="G144" s="30"/>
     </row>
     <row r="145">
-      <c r="G145" s="25"/>
+      <c r="G145" s="30"/>
     </row>
     <row r="146">
-      <c r="G146" s="25"/>
+      <c r="G146" s="30"/>
     </row>
     <row r="147">
-      <c r="G147" s="25"/>
+      <c r="G147" s="30"/>
     </row>
     <row r="148">
-      <c r="G148" s="25"/>
+      <c r="G148" s="30"/>
     </row>
     <row r="149">
-      <c r="G149" s="25"/>
+      <c r="G149" s="30"/>
     </row>
     <row r="150">
-      <c r="G150" s="25"/>
+      <c r="G150" s="30"/>
     </row>
     <row r="151">
-      <c r="G151" s="25"/>
+      <c r="G151" s="30"/>
     </row>
     <row r="152">
-      <c r="G152" s="25"/>
+      <c r="G152" s="30"/>
     </row>
     <row r="153">
-      <c r="G153" s="25"/>
+      <c r="G153" s="30"/>
     </row>
     <row r="154">
-      <c r="G154" s="25"/>
+      <c r="G154" s="30"/>
     </row>
     <row r="155">
-      <c r="G155" s="25"/>
+      <c r="G155" s="30"/>
     </row>
     <row r="156">
-      <c r="G156" s="25"/>
+      <c r="G156" s="30"/>
     </row>
     <row r="157">
-      <c r="G157" s="25"/>
+      <c r="G157" s="30"/>
     </row>
     <row r="158">
-      <c r="G158" s="25"/>
+      <c r="G158" s="30"/>
     </row>
     <row r="159">
-      <c r="G159" s="25"/>
+      <c r="G159" s="30"/>
     </row>
     <row r="160">
-      <c r="G160" s="25"/>
+      <c r="G160" s="30"/>
     </row>
     <row r="161">
-      <c r="G161" s="25"/>
+      <c r="G161" s="30"/>
     </row>
     <row r="162">
-      <c r="G162" s="25"/>
+      <c r="G162" s="30"/>
     </row>
     <row r="163">
-      <c r="G163" s="25"/>
+      <c r="G163" s="30"/>
     </row>
     <row r="164">
-      <c r="G164" s="25"/>
+      <c r="G164" s="30"/>
     </row>
     <row r="165">
-      <c r="G165" s="25"/>
+      <c r="G165" s="30"/>
     </row>
     <row r="166">
-      <c r="G166" s="25"/>
+      <c r="G166" s="30"/>
     </row>
     <row r="167">
-      <c r="G167" s="25"/>
+      <c r="G167" s="30"/>
     </row>
     <row r="168">
-      <c r="G168" s="25"/>
+      <c r="G168" s="30"/>
     </row>
     <row r="169">
-      <c r="G169" s="25"/>
+      <c r="G169" s="30"/>
     </row>
     <row r="170">
-      <c r="G170" s="25"/>
+      <c r="G170" s="30"/>
     </row>
     <row r="171">
-      <c r="G171" s="25"/>
+      <c r="G171" s="30"/>
     </row>
     <row r="172">
-      <c r="G172" s="25"/>
+      <c r="G172" s="30"/>
     </row>
     <row r="173">
-      <c r="G173" s="25"/>
+      <c r="G173" s="30"/>
     </row>
     <row r="174">
-      <c r="G174" s="25"/>
+      <c r="G174" s="30"/>
     </row>
     <row r="175">
-      <c r="G175" s="25"/>
+      <c r="G175" s="30"/>
     </row>
     <row r="176">
-      <c r="G176" s="25"/>
+      <c r="G176" s="30"/>
     </row>
     <row r="177">
-      <c r="G177" s="25"/>
+      <c r="G177" s="30"/>
     </row>
     <row r="178">
-      <c r="G178" s="25"/>
+      <c r="G178" s="30"/>
     </row>
     <row r="179">
-      <c r="G179" s="25"/>
+      <c r="G179" s="30"/>
     </row>
     <row r="180">
-      <c r="G180" s="25"/>
+      <c r="G180" s="30"/>
     </row>
     <row r="181">
-      <c r="G181" s="25"/>
+      <c r="G181" s="30"/>
     </row>
     <row r="182">
-      <c r="G182" s="25"/>
+      <c r="G182" s="30"/>
     </row>
     <row r="183">
-      <c r="G183" s="25"/>
+      <c r="G183" s="30"/>
     </row>
     <row r="184">
-      <c r="G184" s="25"/>
+      <c r="G184" s="30"/>
     </row>
     <row r="185">
-      <c r="G185" s="25"/>
+      <c r="G185" s="30"/>
     </row>
     <row r="186">
-      <c r="G186" s="25"/>
+      <c r="G186" s="30"/>
     </row>
     <row r="187">
-      <c r="G187" s="25"/>
+      <c r="G187" s="30"/>
     </row>
     <row r="188">
-      <c r="G188" s="25"/>
+      <c r="G188" s="30"/>
     </row>
     <row r="189">
-      <c r="G189" s="25"/>
+      <c r="G189" s="30"/>
     </row>
     <row r="190">
-      <c r="G190" s="25"/>
+      <c r="G190" s="30"/>
     </row>
     <row r="191">
-      <c r="G191" s="25"/>
+      <c r="G191" s="30"/>
     </row>
     <row r="192">
-      <c r="G192" s="25"/>
+      <c r="G192" s="30"/>
     </row>
     <row r="193">
-      <c r="G193" s="25"/>
+      <c r="G193" s="30"/>
     </row>
     <row r="194">
-      <c r="G194" s="25"/>
+      <c r="G194" s="30"/>
     </row>
     <row r="195">
-      <c r="G195" s="25"/>
+      <c r="G195" s="30"/>
     </row>
     <row r="196">
-      <c r="G196" s="25"/>
+      <c r="G196" s="30"/>
     </row>
     <row r="197">
-      <c r="G197" s="25"/>
+      <c r="G197" s="30"/>
     </row>
     <row r="198">
-      <c r="G198" s="25"/>
+      <c r="G198" s="30"/>
     </row>
     <row r="199">
-      <c r="G199" s="25"/>
+      <c r="G199" s="30"/>
     </row>
     <row r="200">
-      <c r="G200" s="25"/>
+      <c r="G200" s="30"/>
     </row>
     <row r="201">
-      <c r="G201" s="25"/>
+      <c r="G201" s="30"/>
     </row>
     <row r="202">
-      <c r="G202" s="25"/>
+      <c r="G202" s="30"/>
     </row>
     <row r="203">
-      <c r="G203" s="25"/>
+      <c r="G203" s="30"/>
     </row>
     <row r="204">
-      <c r="G204" s="25"/>
+      <c r="G204" s="30"/>
     </row>
     <row r="205">
-      <c r="G205" s="25"/>
+      <c r="G205" s="30"/>
     </row>
     <row r="206">
-      <c r="G206" s="25"/>
+      <c r="G206" s="30"/>
     </row>
     <row r="207">
-      <c r="G207" s="25"/>
+      <c r="G207" s="30"/>
     </row>
     <row r="208">
-      <c r="G208" s="25"/>
+      <c r="G208" s="30"/>
     </row>
     <row r="209">
-      <c r="G209" s="25"/>
+      <c r="G209" s="30"/>
     </row>
     <row r="210">
-      <c r="G210" s="25"/>
+      <c r="G210" s="30"/>
     </row>
     <row r="211">
-      <c r="G211" s="25"/>
+      <c r="G211" s="30"/>
     </row>
     <row r="212">
-      <c r="G212" s="25"/>
+      <c r="G212" s="30"/>
     </row>
     <row r="213">
-      <c r="G213" s="25"/>
+      <c r="G213" s="30"/>
     </row>
     <row r="214">
-      <c r="G214" s="25"/>
+      <c r="G214" s="30"/>
     </row>
     <row r="215">
-      <c r="G215" s="25"/>
+      <c r="G215" s="30"/>
     </row>
     <row r="216">
-      <c r="G216" s="25"/>
+      <c r="G216" s="30"/>
     </row>
     <row r="217">
-      <c r="G217" s="25"/>
+      <c r="G217" s="30"/>
     </row>
     <row r="218">
-      <c r="G218" s="25"/>
+      <c r="G218" s="30"/>
     </row>
     <row r="219">
-      <c r="G219" s="25"/>
+      <c r="G219" s="30"/>
     </row>
     <row r="220">
-      <c r="G220" s="25"/>
+      <c r="G220" s="30"/>
     </row>
     <row r="221">
-      <c r="G221" s="25"/>
+      <c r="G221" s="30"/>
     </row>
     <row r="222">
-      <c r="G222" s="25"/>
+      <c r="G222" s="30"/>
     </row>
     <row r="223">
-      <c r="G223" s="25"/>
+      <c r="G223" s="30"/>
     </row>
     <row r="224">
-      <c r="G224" s="25"/>
+      <c r="G224" s="30"/>
     </row>
     <row r="225">
-      <c r="G225" s="25"/>
+      <c r="G225" s="30"/>
     </row>
     <row r="226">
-      <c r="G226" s="25"/>
+      <c r="G226" s="30"/>
     </row>
     <row r="227">
-      <c r="G227" s="25"/>
+      <c r="G227" s="30"/>
     </row>
     <row r="228">
-      <c r="G228" s="25"/>
+      <c r="G228" s="30"/>
     </row>
     <row r="229">
-      <c r="G229" s="25"/>
+      <c r="G229" s="30"/>
     </row>
     <row r="230">
-      <c r="G230" s="25"/>
+      <c r="G230" s="30"/>
     </row>
     <row r="231">
-      <c r="G231" s="25"/>
+      <c r="G231" s="30"/>
     </row>
     <row r="232">
-      <c r="G232" s="25"/>
+      <c r="G232" s="30"/>
     </row>
     <row r="233">
-      <c r="G233" s="25"/>
+      <c r="G233" s="30"/>
     </row>
     <row r="234">
-      <c r="G234" s="25"/>
+      <c r="G234" s="30"/>
     </row>
     <row r="235">
-      <c r="G235" s="25"/>
+      <c r="G235" s="30"/>
     </row>
     <row r="236">
-      <c r="G236" s="25"/>
+      <c r="G236" s="30"/>
     </row>
     <row r="237">
-      <c r="G237" s="25"/>
+      <c r="G237" s="30"/>
     </row>
     <row r="238">
-      <c r="G238" s="25"/>
+      <c r="G238" s="30"/>
     </row>
     <row r="239">
-      <c r="G239" s="25"/>
+      <c r="G239" s="30"/>
     </row>
     <row r="240">
-      <c r="G240" s="25"/>
+      <c r="G240" s="30"/>
     </row>
     <row r="241">
-      <c r="G241" s="25"/>
+      <c r="G241" s="30"/>
     </row>
     <row r="242">
-      <c r="G242" s="25"/>
+      <c r="G242" s="30"/>
     </row>
     <row r="243">
-      <c r="G243" s="25"/>
+      <c r="G243" s="30"/>
     </row>
     <row r="244">
-      <c r="G244" s="25"/>
+      <c r="G244" s="30"/>
     </row>
     <row r="245">
-      <c r="G245" s="25"/>
+      <c r="G245" s="30"/>
     </row>
     <row r="246">
-      <c r="G246" s="25"/>
+      <c r="G246" s="30"/>
     </row>
     <row r="247">
-      <c r="G247" s="25"/>
+      <c r="G247" s="30"/>
     </row>
     <row r="248">
-      <c r="G248" s="25"/>
+      <c r="G248" s="30"/>
     </row>
     <row r="249">
-      <c r="G249" s="25"/>
+      <c r="G249" s="30"/>
     </row>
     <row r="250">
-      <c r="G250" s="25"/>
+      <c r="G250" s="30"/>
     </row>
     <row r="251">
-      <c r="G251" s="25"/>
+      <c r="G251" s="30"/>
     </row>
     <row r="252">
-      <c r="G252" s="25"/>
+      <c r="G252" s="30"/>
     </row>
     <row r="253">
-      <c r="G253" s="25"/>
+      <c r="G253" s="30"/>
     </row>
     <row r="254">
-      <c r="G254" s="25"/>
+      <c r="G254" s="30"/>
     </row>
     <row r="255">
-      <c r="G255" s="25"/>
+      <c r="G255" s="30"/>
     </row>
     <row r="256">
-      <c r="G256" s="25"/>
+      <c r="G256" s="30"/>
     </row>
     <row r="257">
-      <c r="G257" s="25"/>
+      <c r="G257" s="30"/>
     </row>
     <row r="258">
-      <c r="G258" s="25"/>
+      <c r="G258" s="30"/>
     </row>
     <row r="259">
-      <c r="G259" s="25"/>
+      <c r="G259" s="30"/>
     </row>
     <row r="260">
-      <c r="G260" s="25"/>
+      <c r="G260" s="30"/>
     </row>
     <row r="261">
-      <c r="G261" s="25"/>
+      <c r="G261" s="30"/>
     </row>
     <row r="262">
-      <c r="G262" s="25"/>
+      <c r="G262" s="30"/>
     </row>
     <row r="263">
-      <c r="G263" s="25"/>
+      <c r="G263" s="30"/>
     </row>
     <row r="264">
-      <c r="G264" s="25"/>
+      <c r="G264" s="30"/>
     </row>
     <row r="265">
-      <c r="G265" s="25"/>
+      <c r="G265" s="30"/>
     </row>
     <row r="266">
-      <c r="G266" s="25"/>
+      <c r="G266" s="30"/>
     </row>
     <row r="267">
-      <c r="G267" s="25"/>
+      <c r="G267" s="30"/>
     </row>
     <row r="268">
-      <c r="G268" s="25"/>
+      <c r="G268" s="30"/>
     </row>
     <row r="269">
-      <c r="G269" s="25"/>
+      <c r="G269" s="30"/>
     </row>
     <row r="270">
-      <c r="G270" s="25"/>
+      <c r="G270" s="30"/>
     </row>
     <row r="271">
-      <c r="G271" s="25"/>
+      <c r="G271" s="30"/>
     </row>
     <row r="272">
-      <c r="G272" s="25"/>
+      <c r="G272" s="30"/>
     </row>
     <row r="273">
-      <c r="G273" s="25"/>
+      <c r="G273" s="30"/>
     </row>
     <row r="274">
-      <c r="G274" s="25"/>
+      <c r="G274" s="30"/>
     </row>
     <row r="275">
-      <c r="G275" s="25"/>
+      <c r="G275" s="30"/>
     </row>
     <row r="276">
-      <c r="G276" s="25"/>
+      <c r="G276" s="30"/>
     </row>
     <row r="277">
-      <c r="G277" s="25"/>
+      <c r="G277" s="30"/>
     </row>
     <row r="278">
-      <c r="G278" s="25"/>
+      <c r="G278" s="30"/>
     </row>
     <row r="279">
-      <c r="G279" s="25"/>
+      <c r="G279" s="30"/>
     </row>
     <row r="280">
-      <c r="G280" s="25"/>
+      <c r="G280" s="30"/>
     </row>
     <row r="281">
-      <c r="G281" s="25"/>
+      <c r="G281" s="30"/>
     </row>
     <row r="282">
-      <c r="G282" s="25"/>
+      <c r="G282" s="30"/>
     </row>
     <row r="283">
-      <c r="G283" s="25"/>
+      <c r="G283" s="30"/>
     </row>
     <row r="284">
-      <c r="G284" s="25"/>
+      <c r="G284" s="30"/>
     </row>
     <row r="285">
-      <c r="G285" s="25"/>
+      <c r="G285" s="30"/>
     </row>
     <row r="286">
-      <c r="G286" s="25"/>
+      <c r="G286" s="30"/>
     </row>
     <row r="287">
-      <c r="G287" s="25"/>
+      <c r="G287" s="30"/>
     </row>
     <row r="288">
-      <c r="G288" s="25"/>
+      <c r="G288" s="30"/>
     </row>
     <row r="289">
-      <c r="G289" s="25"/>
+      <c r="G289" s="30"/>
     </row>
     <row r="290">
-      <c r="G290" s="25"/>
+      <c r="G290" s="30"/>
     </row>
     <row r="291">
-      <c r="G291" s="25"/>
+      <c r="G291" s="30"/>
     </row>
     <row r="292">
-      <c r="G292" s="25"/>
+      <c r="G292" s="30"/>
     </row>
     <row r="293">
-      <c r="G293" s="25"/>
+      <c r="G293" s="30"/>
     </row>
     <row r="294">
-      <c r="G294" s="25"/>
+      <c r="G294" s="30"/>
     </row>
     <row r="295">
-      <c r="G295" s="25"/>
+      <c r="G295" s="30"/>
     </row>
     <row r="296">
-      <c r="G296" s="25"/>
+      <c r="G296" s="30"/>
     </row>
     <row r="297">
-      <c r="G297" s="25"/>
+      <c r="G297" s="30"/>
     </row>
     <row r="298">
-      <c r="G298" s="25"/>
+      <c r="G298" s="30"/>
     </row>
     <row r="299">
-      <c r="G299" s="25"/>
+      <c r="G299" s="30"/>
     </row>
     <row r="300">
-      <c r="G300" s="25"/>
+      <c r="G300" s="30"/>
     </row>
     <row r="301">
-      <c r="G301" s="25"/>
+      <c r="G301" s="30"/>
     </row>
     <row r="302">
-      <c r="G302" s="25"/>
+      <c r="G302" s="30"/>
     </row>
     <row r="303">
-      <c r="G303" s="25"/>
+      <c r="G303" s="30"/>
     </row>
     <row r="304">
-      <c r="G304" s="25"/>
+      <c r="G304" s="30"/>
     </row>
     <row r="305">
-      <c r="G305" s="25"/>
+      <c r="G305" s="30"/>
     </row>
     <row r="306">
-      <c r="G306" s="25"/>
+      <c r="G306" s="30"/>
     </row>
     <row r="307">
-      <c r="G307" s="25"/>
+      <c r="G307" s="30"/>
     </row>
     <row r="308">
-      <c r="G308" s="25"/>
+      <c r="G308" s="30"/>
     </row>
     <row r="309">
-      <c r="G309" s="25"/>
+      <c r="G309" s="30"/>
     </row>
     <row r="310">
-      <c r="G310" s="25"/>
+      <c r="G310" s="30"/>
     </row>
     <row r="311">
-      <c r="G311" s="25"/>
+      <c r="G311" s="30"/>
     </row>
     <row r="312">
-      <c r="G312" s="25"/>
+      <c r="G312" s="30"/>
     </row>
     <row r="313">
-      <c r="G313" s="25"/>
+      <c r="G313" s="30"/>
     </row>
     <row r="314">
-      <c r="G314" s="25"/>
+      <c r="G314" s="30"/>
     </row>
     <row r="315">
-      <c r="G315" s="25"/>
+      <c r="G315" s="30"/>
     </row>
     <row r="316">
-      <c r="G316" s="25"/>
+      <c r="G316" s="30"/>
     </row>
     <row r="317">
-      <c r="G317" s="25"/>
+      <c r="G317" s="30"/>
     </row>
     <row r="318">
-      <c r="G318" s="25"/>
+      <c r="G318" s="30"/>
     </row>
     <row r="319">
-      <c r="G319" s="25"/>
+      <c r="G319" s="30"/>
     </row>
     <row r="320">
-      <c r="G320" s="25"/>
+      <c r="G320" s="30"/>
     </row>
     <row r="321">
-      <c r="G321" s="25"/>
+      <c r="G321" s="30"/>
     </row>
     <row r="322">
-      <c r="G322" s="25"/>
+      <c r="G322" s="30"/>
     </row>
     <row r="323">
-      <c r="G323" s="25"/>
+      <c r="G323" s="30"/>
     </row>
     <row r="324">
-      <c r="G324" s="25"/>
+      <c r="G324" s="30"/>
     </row>
     <row r="325">
-      <c r="G325" s="25"/>
+      <c r="G325" s="30"/>
     </row>
     <row r="326">
-      <c r="G326" s="25"/>
+      <c r="G326" s="30"/>
     </row>
     <row r="327">
-      <c r="G327" s="25"/>
+      <c r="G327" s="30"/>
     </row>
     <row r="328">
-      <c r="G328" s="25"/>
+      <c r="G328" s="30"/>
     </row>
     <row r="329">
-      <c r="G329" s="25"/>
+      <c r="G329" s="30"/>
     </row>
     <row r="330">
-      <c r="G330" s="25"/>
+      <c r="G330" s="30"/>
     </row>
     <row r="331">
-      <c r="G331" s="25"/>
+      <c r="G331" s="30"/>
     </row>
     <row r="332">
-      <c r="G332" s="25"/>
+      <c r="G332" s="30"/>
     </row>
     <row r="333">
-      <c r="G333" s="25"/>
+      <c r="G333" s="30"/>
     </row>
     <row r="334">
-      <c r="G334" s="25"/>
+      <c r="G334" s="30"/>
     </row>
     <row r="335">
-      <c r="G335" s="25"/>
+      <c r="G335" s="30"/>
     </row>
     <row r="336">
-      <c r="G336" s="25"/>
+      <c r="G336" s="30"/>
     </row>
     <row r="337">
-      <c r="G337" s="25"/>
+      <c r="G337" s="30"/>
     </row>
     <row r="338">
-      <c r="G338" s="25"/>
+      <c r="G338" s="30"/>
     </row>
     <row r="339">
-      <c r="G339" s="25"/>
+      <c r="G339" s="30"/>
     </row>
     <row r="340">
-      <c r="G340" s="25"/>
+      <c r="G340" s="30"/>
     </row>
     <row r="341">
-      <c r="G341" s="25"/>
+      <c r="G341" s="30"/>
     </row>
     <row r="342">
-      <c r="G342" s="25"/>
+      <c r="G342" s="30"/>
     </row>
     <row r="343">
-      <c r="G343" s="25"/>
+      <c r="G343" s="30"/>
     </row>
     <row r="344">
-      <c r="G344" s="25"/>
+      <c r="G344" s="30"/>
     </row>
     <row r="345">
-      <c r="G345" s="25"/>
+      <c r="G345" s="30"/>
     </row>
     <row r="346">
-      <c r="G346" s="25"/>
+      <c r="G346" s="30"/>
     </row>
     <row r="347">
-      <c r="G347" s="25"/>
+      <c r="G347" s="30"/>
     </row>
     <row r="348">
-      <c r="G348" s="25"/>
+      <c r="G348" s="30"/>
     </row>
     <row r="349">
-      <c r="G349" s="25"/>
+      <c r="G349" s="30"/>
     </row>
     <row r="350">
-      <c r="G350" s="25"/>
+      <c r="G350" s="30"/>
     </row>
     <row r="351">
-      <c r="G351" s="25"/>
+      <c r="G351" s="30"/>
     </row>
     <row r="352">
-      <c r="G352" s="25"/>
+      <c r="G352" s="30"/>
     </row>
     <row r="353">
-      <c r="G353" s="25"/>
+      <c r="G353" s="30"/>
     </row>
     <row r="354">
-      <c r="G354" s="25"/>
+      <c r="G354" s="30"/>
     </row>
     <row r="355">
-      <c r="G355" s="25"/>
+      <c r="G355" s="30"/>
     </row>
     <row r="356">
-      <c r="G356" s="25"/>
+      <c r="G356" s="30"/>
     </row>
     <row r="357">
-      <c r="G357" s="25"/>
+      <c r="G357" s="30"/>
     </row>
     <row r="358">
-      <c r="G358" s="25"/>
+      <c r="G358" s="30"/>
     </row>
     <row r="359">
-      <c r="G359" s="25"/>
+      <c r="G359" s="30"/>
     </row>
     <row r="360">
-      <c r="G360" s="25"/>
+      <c r="G360" s="30"/>
     </row>
     <row r="361">
-      <c r="G361" s="25"/>
+      <c r="G361" s="30"/>
     </row>
     <row r="362">
-      <c r="G362" s="25"/>
+      <c r="G362" s="30"/>
     </row>
     <row r="363">
-      <c r="G363" s="25"/>
+      <c r="G363" s="30"/>
     </row>
     <row r="364">
-      <c r="G364" s="25"/>
+      <c r="G364" s="30"/>
     </row>
     <row r="365">
-      <c r="G365" s="25"/>
+      <c r="G365" s="30"/>
     </row>
     <row r="366">
-      <c r="G366" s="25"/>
+      <c r="G366" s="30"/>
     </row>
     <row r="367">
-      <c r="G367" s="25"/>
+      <c r="G367" s="30"/>
     </row>
     <row r="368">
-      <c r="G368" s="25"/>
+      <c r="G368" s="30"/>
     </row>
     <row r="369">
-      <c r="G369" s="25"/>
+      <c r="G369" s="30"/>
     </row>
     <row r="370">
-      <c r="G370" s="25"/>
+      <c r="G370" s="30"/>
     </row>
     <row r="371">
-      <c r="G371" s="25"/>
+      <c r="G371" s="30"/>
     </row>
     <row r="372">
-      <c r="G372" s="25"/>
+      <c r="G372" s="30"/>
     </row>
     <row r="373">
-      <c r="G373" s="25"/>
+      <c r="G373" s="30"/>
     </row>
     <row r="374">
-      <c r="G374" s="25"/>
+      <c r="G374" s="30"/>
     </row>
     <row r="375">
-      <c r="G375" s="25"/>
+      <c r="G375" s="30"/>
     </row>
     <row r="376">
-      <c r="G376" s="25"/>
+      <c r="G376" s="30"/>
     </row>
     <row r="377">
-      <c r="G377" s="25"/>
+      <c r="G377" s="30"/>
     </row>
     <row r="378">
-      <c r="G378" s="25"/>
+      <c r="G378" s="30"/>
     </row>
     <row r="379">
-      <c r="G379" s="25"/>
+      <c r="G379" s="30"/>
     </row>
     <row r="380">
-      <c r="G380" s="25"/>
+      <c r="G380" s="30"/>
     </row>
     <row r="381">
-      <c r="G381" s="25"/>
+      <c r="G381" s="30"/>
     </row>
     <row r="382">
-      <c r="G382" s="25"/>
+      <c r="G382" s="30"/>
     </row>
     <row r="383">
-      <c r="G383" s="25"/>
+      <c r="G383" s="30"/>
     </row>
     <row r="384">
-      <c r="G384" s="25"/>
+      <c r="G384" s="30"/>
     </row>
     <row r="385">
-      <c r="G385" s="25"/>
+      <c r="G385" s="30"/>
     </row>
     <row r="386">
-      <c r="G386" s="25"/>
+      <c r="G386" s="30"/>
     </row>
     <row r="387">
-      <c r="G387" s="25"/>
+      <c r="G387" s="30"/>
     </row>
     <row r="388">
-      <c r="G388" s="25"/>
+      <c r="G388" s="30"/>
     </row>
     <row r="389">
-      <c r="G389" s="25"/>
+      <c r="G389" s="30"/>
     </row>
     <row r="390">
-      <c r="G390" s="25"/>
+      <c r="G390" s="30"/>
     </row>
     <row r="391">
-      <c r="G391" s="25"/>
+      <c r="G391" s="30"/>
     </row>
     <row r="392">
-      <c r="G392" s="25"/>
+      <c r="G392" s="30"/>
     </row>
     <row r="393">
-      <c r="G393" s="25"/>
+      <c r="G393" s="30"/>
     </row>
     <row r="394">
-      <c r="G394" s="25"/>
+      <c r="G394" s="30"/>
     </row>
     <row r="395">
-      <c r="G395" s="25"/>
+      <c r="G395" s="30"/>
     </row>
     <row r="396">
-      <c r="G396" s="25"/>
+      <c r="G396" s="30"/>
     </row>
     <row r="397">
-      <c r="G397" s="25"/>
+      <c r="G397" s="30"/>
     </row>
     <row r="398">
-      <c r="G398" s="25"/>
+      <c r="G398" s="30"/>
     </row>
     <row r="399">
-      <c r="G399" s="25"/>
+      <c r="G399" s="30"/>
     </row>
     <row r="400">
-      <c r="G400" s="25"/>
+      <c r="G400" s="30"/>
     </row>
     <row r="401">
-      <c r="G401" s="25"/>
+      <c r="G401" s="30"/>
     </row>
     <row r="402">
-      <c r="G402" s="25"/>
+      <c r="G402" s="30"/>
     </row>
     <row r="403">
-      <c r="G403" s="25"/>
+      <c r="G403" s="30"/>
     </row>
     <row r="404">
-      <c r="G404" s="25"/>
+      <c r="G404" s="30"/>
     </row>
     <row r="405">
-      <c r="G405" s="25"/>
+      <c r="G405" s="30"/>
     </row>
     <row r="406">
-      <c r="G406" s="25"/>
+      <c r="G406" s="30"/>
     </row>
     <row r="407">
-      <c r="G407" s="25"/>
+      <c r="G407" s="30"/>
     </row>
     <row r="408">
-      <c r="G408" s="25"/>
+      <c r="G408" s="30"/>
     </row>
     <row r="409">
-      <c r="G409" s="25"/>
+      <c r="G409" s="30"/>
     </row>
     <row r="410">
-      <c r="G410" s="25"/>
+      <c r="G410" s="30"/>
     </row>
     <row r="411">
-      <c r="G411" s="25"/>
+      <c r="G411" s="30"/>
     </row>
     <row r="412">
-      <c r="G412" s="25"/>
+      <c r="G412" s="30"/>
     </row>
     <row r="413">
-      <c r="G413" s="25"/>
+      <c r="G413" s="30"/>
     </row>
     <row r="414">
-      <c r="G414" s="25"/>
+      <c r="G414" s="30"/>
     </row>
     <row r="415">
-      <c r="G415" s="25"/>
+      <c r="G415" s="30"/>
     </row>
     <row r="416">
-      <c r="G416" s="25"/>
+      <c r="G416" s="30"/>
     </row>
     <row r="417">
-      <c r="G417" s="25"/>
+      <c r="G417" s="30"/>
     </row>
     <row r="418">
-      <c r="G418" s="25"/>
+      <c r="G418" s="30"/>
     </row>
     <row r="419">
-      <c r="G419" s="25"/>
+      <c r="G419" s="30"/>
     </row>
     <row r="420">
-      <c r="G420" s="25"/>
+      <c r="G420" s="30"/>
     </row>
     <row r="421">
-      <c r="G421" s="25"/>
+      <c r="G421" s="30"/>
     </row>
     <row r="422">
-      <c r="G422" s="25"/>
+      <c r="G422" s="30"/>
     </row>
     <row r="423">
-      <c r="G423" s="25"/>
+      <c r="G423" s="30"/>
     </row>
     <row r="424">
-      <c r="G424" s="25"/>
+      <c r="G424" s="30"/>
     </row>
     <row r="425">
-      <c r="G425" s="25"/>
+      <c r="G425" s="30"/>
     </row>
     <row r="426">
-      <c r="G426" s="25"/>
+      <c r="G426" s="30"/>
     </row>
     <row r="427">
-      <c r="G427" s="25"/>
+      <c r="G427" s="30"/>
     </row>
     <row r="428">
-      <c r="G428" s="25"/>
+      <c r="G428" s="30"/>
     </row>
     <row r="429">
-      <c r="G429" s="25"/>
+      <c r="G429" s="30"/>
     </row>
     <row r="430">
-      <c r="G430" s="25"/>
+      <c r="G430" s="30"/>
     </row>
     <row r="431">
-      <c r="G431" s="25"/>
+      <c r="G431" s="30"/>
     </row>
     <row r="432">
-      <c r="G432" s="25"/>
+      <c r="G432" s="30"/>
     </row>
     <row r="433">
-      <c r="G433" s="25"/>
+      <c r="G433" s="30"/>
     </row>
     <row r="434">
-      <c r="G434" s="25"/>
+      <c r="G434" s="30"/>
     </row>
     <row r="435">
-      <c r="G435" s="25"/>
+      <c r="G435" s="30"/>
     </row>
     <row r="436">
-      <c r="G436" s="25"/>
+      <c r="G436" s="30"/>
     </row>
     <row r="437">
-      <c r="G437" s="25"/>
+      <c r="G437" s="30"/>
     </row>
     <row r="438">
-      <c r="G438" s="25"/>
+      <c r="G438" s="30"/>
     </row>
     <row r="439">
-      <c r="G439" s="25"/>
+      <c r="G439" s="30"/>
     </row>
     <row r="440">
-      <c r="G440" s="25"/>
+      <c r="G440" s="30"/>
     </row>
     <row r="441">
-      <c r="G441" s="25"/>
+      <c r="G441" s="30"/>
     </row>
     <row r="442">
-      <c r="G442" s="25"/>
+      <c r="G442" s="30"/>
     </row>
     <row r="443">
-      <c r="G443" s="25"/>
+      <c r="G443" s="30"/>
     </row>
     <row r="444">
-      <c r="G444" s="25"/>
+      <c r="G444" s="30"/>
     </row>
     <row r="445">
-      <c r="G445" s="25"/>
+      <c r="G445" s="30"/>
     </row>
     <row r="446">
-      <c r="G446" s="25"/>
+      <c r="G446" s="30"/>
     </row>
     <row r="447">
-      <c r="G447" s="25"/>
+      <c r="G447" s="30"/>
     </row>
     <row r="448">
-      <c r="G448" s="25"/>
+      <c r="G448" s="30"/>
     </row>
     <row r="449">
-      <c r="G449" s="25"/>
+      <c r="G449" s="30"/>
     </row>
     <row r="450">
-      <c r="G450" s="25"/>
+      <c r="G450" s="30"/>
     </row>
     <row r="451">
-      <c r="G451" s="25"/>
+      <c r="G451" s="30"/>
     </row>
     <row r="452">
-      <c r="G452" s="25"/>
+      <c r="G452" s="30"/>
     </row>
     <row r="453">
-      <c r="G453" s="25"/>
+      <c r="G453" s="30"/>
     </row>
     <row r="454">
-      <c r="G454" s="25"/>
+      <c r="G454" s="30"/>
     </row>
     <row r="455">
-      <c r="G455" s="25"/>
+      <c r="G455" s="30"/>
     </row>
     <row r="456">
-      <c r="G456" s="25"/>
+      <c r="G456" s="30"/>
     </row>
     <row r="457">
-      <c r="G457" s="25"/>
+      <c r="G457" s="30"/>
     </row>
     <row r="458">
-      <c r="G458" s="25"/>
+      <c r="G458" s="30"/>
     </row>
     <row r="459">
-      <c r="G459" s="25"/>
+      <c r="G459" s="30"/>
     </row>
     <row r="460">
-      <c r="G460" s="25"/>
+      <c r="G460" s="30"/>
     </row>
     <row r="461">
-      <c r="G461" s="25"/>
+      <c r="G461" s="30"/>
     </row>
     <row r="462">
-      <c r="G462" s="25"/>
+      <c r="G462" s="30"/>
     </row>
     <row r="463">
-      <c r="G463" s="25"/>
+      <c r="G463" s="30"/>
     </row>
     <row r="464">
-      <c r="G464" s="25"/>
+      <c r="G464" s="30"/>
     </row>
     <row r="465">
-      <c r="G465" s="25"/>
+      <c r="G465" s="30"/>
     </row>
     <row r="466">
-      <c r="G466" s="25"/>
+      <c r="G466" s="30"/>
     </row>
     <row r="467">
-      <c r="G467" s="25"/>
+      <c r="G467" s="30"/>
     </row>
     <row r="468">
-      <c r="G468" s="25"/>
+      <c r="G468" s="30"/>
     </row>
     <row r="469">
-      <c r="G469" s="25"/>
+      <c r="G469" s="30"/>
     </row>
     <row r="470">
-      <c r="G470" s="25"/>
+      <c r="G470" s="30"/>
     </row>
     <row r="471">
-      <c r="G471" s="25"/>
+      <c r="G471" s="30"/>
     </row>
     <row r="472">
-      <c r="G472" s="25"/>
+      <c r="G472" s="30"/>
     </row>
     <row r="473">
-      <c r="G473" s="25"/>
+      <c r="G473" s="30"/>
     </row>
     <row r="474">
-      <c r="G474" s="25"/>
+      <c r="G474" s="30"/>
     </row>
     <row r="475">
-      <c r="G475" s="25"/>
+      <c r="G475" s="30"/>
     </row>
     <row r="476">
-      <c r="G476" s="25"/>
+      <c r="G476" s="30"/>
     </row>
     <row r="477">
-      <c r="G477" s="25"/>
+      <c r="G477" s="30"/>
     </row>
     <row r="478">
-      <c r="G478" s="25"/>
+      <c r="G478" s="30"/>
     </row>
     <row r="479">
-      <c r="G479" s="25"/>
+      <c r="G479" s="30"/>
     </row>
     <row r="480">
-      <c r="G480" s="25"/>
+      <c r="G480" s="30"/>
     </row>
     <row r="481">
-      <c r="G481" s="25"/>
+      <c r="G481" s="30"/>
     </row>
     <row r="482">
-      <c r="G482" s="25"/>
+      <c r="G482" s="30"/>
     </row>
     <row r="483">
-      <c r="G483" s="25"/>
+      <c r="G483" s="30"/>
     </row>
     <row r="484">
-      <c r="G484" s="25"/>
+      <c r="G484" s="30"/>
     </row>
     <row r="485">
-      <c r="G485" s="25"/>
+      <c r="G485" s="30"/>
     </row>
     <row r="486">
-      <c r="G486" s="25"/>
+      <c r="G486" s="30"/>
     </row>
     <row r="487">
-      <c r="G487" s="25"/>
+      <c r="G487" s="30"/>
     </row>
     <row r="488">
-      <c r="G488" s="25"/>
+      <c r="G488" s="30"/>
     </row>
     <row r="489">
-      <c r="G489" s="25"/>
+      <c r="G489" s="30"/>
     </row>
     <row r="490">
-      <c r="G490" s="25"/>
+      <c r="G490" s="30"/>
     </row>
     <row r="491">
-      <c r="G491" s="25"/>
+      <c r="G491" s="30"/>
     </row>
     <row r="492">
-      <c r="G492" s="25"/>
+      <c r="G492" s="30"/>
     </row>
     <row r="493">
-      <c r="G493" s="25"/>
+      <c r="G493" s="30"/>
     </row>
     <row r="494">
-      <c r="G494" s="25"/>
+      <c r="G494" s="30"/>
     </row>
     <row r="495">
-      <c r="G495" s="25"/>
+      <c r="G495" s="30"/>
     </row>
     <row r="496">
-      <c r="G496" s="25"/>
+      <c r="G496" s="30"/>
     </row>
     <row r="497">
-      <c r="G497" s="25"/>
+      <c r="G497" s="30"/>
     </row>
     <row r="498">
-      <c r="G498" s="25"/>
+      <c r="G498" s="30"/>
     </row>
     <row r="499">
-      <c r="G499" s="25"/>
+      <c r="G499" s="30"/>
     </row>
     <row r="500">
-      <c r="G500" s="25"/>
+      <c r="G500" s="30"/>
     </row>
     <row r="501">
-      <c r="G501" s="25"/>
+      <c r="G501" s="30"/>
     </row>
     <row r="502">
-      <c r="G502" s="25"/>
+      <c r="G502" s="30"/>
     </row>
     <row r="503">
-      <c r="G503" s="25"/>
+      <c r="G503" s="30"/>
     </row>
     <row r="504">
-      <c r="G504" s="25"/>
+      <c r="G504" s="30"/>
     </row>
     <row r="505">
-      <c r="G505" s="25"/>
+      <c r="G505" s="30"/>
     </row>
     <row r="506">
-      <c r="G506" s="25"/>
+      <c r="G506" s="30"/>
     </row>
     <row r="507">
-      <c r="G507" s="25"/>
+      <c r="G507" s="30"/>
     </row>
     <row r="508">
-      <c r="G508" s="25"/>
+      <c r="G508" s="30"/>
     </row>
     <row r="509">
-      <c r="G509" s="25"/>
+      <c r="G509" s="30"/>
     </row>
     <row r="510">
-      <c r="G510" s="25"/>
+      <c r="G510" s="30"/>
     </row>
     <row r="511">
-      <c r="G511" s="25"/>
+      <c r="G511" s="30"/>
     </row>
     <row r="512">
-      <c r="G512" s="25"/>
+      <c r="G512" s="30"/>
     </row>
     <row r="513">
-      <c r="G513" s="25"/>
+      <c r="G513" s="30"/>
     </row>
     <row r="514">
-      <c r="G514" s="25"/>
+      <c r="G514" s="30"/>
     </row>
     <row r="515">
-      <c r="G515" s="25"/>
+      <c r="G515" s="30"/>
     </row>
     <row r="516">
-      <c r="G516" s="25"/>
+      <c r="G516" s="30"/>
     </row>
     <row r="517">
-      <c r="G517" s="25"/>
+      <c r="G517" s="30"/>
     </row>
     <row r="518">
-      <c r="G518" s="25"/>
+      <c r="G518" s="30"/>
     </row>
     <row r="519">
-      <c r="G519" s="25"/>
+      <c r="G519" s="30"/>
     </row>
     <row r="520">
-      <c r="G520" s="25"/>
+      <c r="G520" s="30"/>
     </row>
     <row r="521">
-      <c r="G521" s="25"/>
+      <c r="G521" s="30"/>
     </row>
     <row r="522">
-      <c r="G522" s="25"/>
+      <c r="G522" s="30"/>
     </row>
     <row r="523">
-      <c r="G523" s="25"/>
+      <c r="G523" s="30"/>
     </row>
     <row r="524">
-      <c r="G524" s="25"/>
+      <c r="G524" s="30"/>
     </row>
     <row r="525">
-      <c r="G525" s="25"/>
+      <c r="G525" s="30"/>
     </row>
     <row r="526">
-      <c r="G526" s="25"/>
+      <c r="G526" s="30"/>
     </row>
     <row r="527">
-      <c r="G527" s="25"/>
+      <c r="G527" s="30"/>
     </row>
     <row r="528">
-      <c r="G528" s="25"/>
+      <c r="G528" s="30"/>
     </row>
     <row r="529">
-      <c r="G529" s="25"/>
+      <c r="G529" s="30"/>
     </row>
     <row r="530">
-      <c r="G530" s="25"/>
+      <c r="G530" s="30"/>
     </row>
     <row r="531">
-      <c r="G531" s="25"/>
+      <c r="G531" s="30"/>
     </row>
     <row r="532">
-      <c r="G532" s="25"/>
+      <c r="G532" s="30"/>
     </row>
     <row r="533">
-      <c r="G533" s="25"/>
+      <c r="G533" s="30"/>
     </row>
     <row r="534">
-      <c r="G534" s="25"/>
+      <c r="G534" s="30"/>
     </row>
     <row r="535">
-      <c r="G535" s="25"/>
+      <c r="G535" s="30"/>
     </row>
     <row r="536">
-      <c r="G536" s="25"/>
+      <c r="G536" s="30"/>
     </row>
     <row r="537">
-      <c r="G537" s="25"/>
+      <c r="G537" s="30"/>
     </row>
     <row r="538">
-      <c r="G538" s="25"/>
+      <c r="G538" s="30"/>
     </row>
     <row r="539">
-      <c r="G539" s="25"/>
+      <c r="G539" s="30"/>
     </row>
     <row r="540">
-      <c r="G540" s="25"/>
+      <c r="G540" s="30"/>
     </row>
     <row r="541">
-      <c r="G541" s="25"/>
+      <c r="G541" s="30"/>
     </row>
     <row r="542">
-      <c r="G542" s="25"/>
+      <c r="G542" s="30"/>
     </row>
     <row r="543">
-      <c r="G543" s="25"/>
+      <c r="G543" s="30"/>
     </row>
     <row r="544">
-      <c r="G544" s="25"/>
+      <c r="G544" s="30"/>
     </row>
     <row r="545">
-      <c r="G545" s="25"/>
+      <c r="G545" s="30"/>
     </row>
     <row r="546">
-      <c r="G546" s="25"/>
+      <c r="G546" s="30"/>
     </row>
     <row r="547">
-      <c r="G547" s="25"/>
+      <c r="G547" s="30"/>
     </row>
     <row r="548">
-      <c r="G548" s="25"/>
+      <c r="G548" s="30"/>
     </row>
     <row r="549">
-      <c r="G549" s="25"/>
+      <c r="G549" s="30"/>
     </row>
     <row r="550">
-      <c r="G550" s="25"/>
+      <c r="G550" s="30"/>
     </row>
     <row r="551">
-      <c r="G551" s="25"/>
+      <c r="G551" s="30"/>
     </row>
     <row r="552">
-      <c r="G552" s="25"/>
+      <c r="G552" s="30"/>
     </row>
     <row r="553">
-      <c r="G553" s="25"/>
+      <c r="G553" s="30"/>
     </row>
     <row r="554">
-      <c r="G554" s="25"/>
+      <c r="G554" s="30"/>
     </row>
     <row r="555">
-      <c r="G555" s="25"/>
+      <c r="G555" s="30"/>
     </row>
     <row r="556">
-      <c r="G556" s="25"/>
+      <c r="G556" s="30"/>
     </row>
     <row r="557">
-      <c r="G557" s="25"/>
+      <c r="G557" s="30"/>
     </row>
     <row r="558">
-      <c r="G558" s="25"/>
+      <c r="G558" s="30"/>
     </row>
     <row r="559">
-      <c r="G559" s="25"/>
+      <c r="G559" s="30"/>
     </row>
     <row r="560">
-      <c r="G560" s="25"/>
+      <c r="G560" s="30"/>
     </row>
     <row r="561">
-      <c r="G561" s="25"/>
+      <c r="G561" s="30"/>
     </row>
     <row r="562">
-      <c r="G562" s="25"/>
+      <c r="G562" s="30"/>
     </row>
     <row r="563">
-      <c r="G563" s="25"/>
+      <c r="G563" s="30"/>
     </row>
     <row r="564">
-      <c r="G564" s="25"/>
+      <c r="G564" s="30"/>
     </row>
     <row r="565">
-      <c r="G565" s="25"/>
+      <c r="G565" s="30"/>
     </row>
     <row r="566">
-      <c r="G566" s="25"/>
+      <c r="G566" s="30"/>
     </row>
     <row r="567">
-      <c r="G567" s="25"/>
+      <c r="G567" s="30"/>
     </row>
     <row r="568">
-      <c r="G568" s="25"/>
+      <c r="G568" s="30"/>
     </row>
     <row r="569">
-      <c r="G569" s="25"/>
+      <c r="G569" s="30"/>
     </row>
     <row r="570">
-      <c r="G570" s="25"/>
+      <c r="G570" s="30"/>
     </row>
     <row r="571">
-      <c r="G571" s="25"/>
+      <c r="G571" s="30"/>
     </row>
     <row r="572">
-      <c r="G572" s="25"/>
+      <c r="G572" s="30"/>
     </row>
     <row r="573">
-      <c r="G573" s="25"/>
+      <c r="G573" s="30"/>
     </row>
     <row r="574">
-      <c r="G574" s="25"/>
+      <c r="G574" s="30"/>
     </row>
     <row r="575">
-      <c r="G575" s="25"/>
+      <c r="G575" s="30"/>
     </row>
     <row r="576">
-      <c r="G576" s="25"/>
+      <c r="G576" s="30"/>
     </row>
     <row r="577">
-      <c r="G577" s="25"/>
+      <c r="G577" s="30"/>
     </row>
     <row r="578">
-      <c r="G578" s="25"/>
+      <c r="G578" s="30"/>
     </row>
     <row r="579">
-      <c r="G579" s="25"/>
+      <c r="G579" s="30"/>
     </row>
     <row r="580">
-      <c r="G580" s="25"/>
+      <c r="G580" s="30"/>
     </row>
     <row r="581">
-      <c r="G581" s="25"/>
+      <c r="G581" s="30"/>
     </row>
     <row r="582">
-      <c r="G582" s="25"/>
+      <c r="G582" s="30"/>
     </row>
     <row r="583">
-      <c r="G583" s="25"/>
+      <c r="G583" s="30"/>
     </row>
     <row r="584">
-      <c r="G584" s="25"/>
+      <c r="G584" s="30"/>
     </row>
     <row r="585">
-      <c r="G585" s="25"/>
+      <c r="G585" s="30"/>
     </row>
     <row r="586">
-      <c r="G586" s="25"/>
+      <c r="G586" s="30"/>
     </row>
     <row r="587">
-      <c r="G587" s="25"/>
+      <c r="G587" s="30"/>
     </row>
     <row r="588">
-      <c r="G588" s="25"/>
+      <c r="G588" s="30"/>
     </row>
     <row r="589">
-      <c r="G589" s="25"/>
+      <c r="G589" s="30"/>
     </row>
     <row r="590">
-      <c r="G590" s="25"/>
+      <c r="G590" s="30"/>
     </row>
     <row r="591">
-      <c r="G591" s="25"/>
+      <c r="G591" s="30"/>
     </row>
     <row r="592">
-      <c r="G592" s="25"/>
+      <c r="G592" s="30"/>
     </row>
     <row r="593">
-      <c r="G593" s="25"/>
+      <c r="G593" s="30"/>
     </row>
     <row r="594">
-      <c r="G594" s="25"/>
+      <c r="G594" s="30"/>
     </row>
     <row r="595">
-      <c r="G595" s="25"/>
+      <c r="G595" s="30"/>
     </row>
     <row r="596">
-      <c r="G596" s="25"/>
+      <c r="G596" s="30"/>
     </row>
     <row r="597">
-      <c r="G597" s="25"/>
+      <c r="G597" s="30"/>
     </row>
     <row r="598">
-      <c r="G598" s="25"/>
+      <c r="G598" s="30"/>
     </row>
     <row r="599">
-      <c r="G599" s="25"/>
+      <c r="G599" s="30"/>
     </row>
     <row r="600">
-      <c r="G600" s="25"/>
+      <c r="G600" s="30"/>
     </row>
     <row r="601">
-      <c r="G601" s="25"/>
+      <c r="G601" s="30"/>
     </row>
     <row r="602">
-      <c r="G602" s="25"/>
+      <c r="G602" s="30"/>
     </row>
     <row r="603">
-      <c r="G603" s="25"/>
+      <c r="G603" s="30"/>
     </row>
     <row r="604">
-      <c r="G604" s="25"/>
+      <c r="G604" s="30"/>
     </row>
     <row r="605">
-      <c r="G605" s="25"/>
+      <c r="G605" s="30"/>
     </row>
     <row r="606">
-      <c r="G606" s="25"/>
+      <c r="G606" s="30"/>
     </row>
     <row r="607">
-      <c r="G607" s="25"/>
+      <c r="G607" s="30"/>
     </row>
     <row r="608">
-      <c r="G608" s="25"/>
+      <c r="G608" s="30"/>
     </row>
     <row r="609">
-      <c r="G609" s="25"/>
+      <c r="G609" s="30"/>
     </row>
     <row r="610">
-      <c r="G610" s="25"/>
+      <c r="G610" s="30"/>
     </row>
     <row r="611">
-      <c r="G611" s="25"/>
+      <c r="G611" s="30"/>
     </row>
     <row r="612">
-      <c r="G612" s="25"/>
+      <c r="G612" s="30"/>
     </row>
     <row r="613">
-      <c r="G613" s="25"/>
+      <c r="G613" s="30"/>
     </row>
     <row r="614">
-      <c r="G614" s="25"/>
+      <c r="G614" s="30"/>
     </row>
     <row r="615">
-      <c r="G615" s="25"/>
+      <c r="G615" s="30"/>
     </row>
     <row r="616">
-      <c r="G616" s="25"/>
+      <c r="G616" s="30"/>
     </row>
     <row r="617">
-      <c r="G617" s="25"/>
+      <c r="G617" s="30"/>
     </row>
     <row r="618">
-      <c r="G618" s="25"/>
+      <c r="G618" s="30"/>
     </row>
     <row r="619">
-      <c r="G619" s="25"/>
+      <c r="G619" s="30"/>
     </row>
     <row r="620">
-      <c r="G620" s="25"/>
+      <c r="G620" s="30"/>
     </row>
     <row r="621">
-      <c r="G621" s="25"/>
+      <c r="G621" s="30"/>
     </row>
     <row r="622">
-      <c r="G622" s="25"/>
+      <c r="G622" s="30"/>
     </row>
     <row r="623">
-      <c r="G623" s="25"/>
+      <c r="G623" s="30"/>
     </row>
     <row r="624">
-      <c r="G624" s="25"/>
+      <c r="G624" s="30"/>
     </row>
     <row r="625">
-      <c r="G625" s="25"/>
+      <c r="G625" s="30"/>
     </row>
     <row r="626">
-      <c r="G626" s="25"/>
+      <c r="G626" s="30"/>
     </row>
     <row r="627">
-      <c r="G627" s="25"/>
+      <c r="G627" s="30"/>
     </row>
     <row r="628">
-      <c r="G628" s="25"/>
+      <c r="G628" s="30"/>
     </row>
     <row r="629">
-      <c r="G629" s="25"/>
+      <c r="G629" s="30"/>
     </row>
     <row r="630">
-      <c r="G630" s="25"/>
+      <c r="G630" s="30"/>
     </row>
     <row r="631">
-      <c r="G631" s="25"/>
+      <c r="G631" s="30"/>
     </row>
     <row r="632">
-      <c r="G632" s="25"/>
+      <c r="G632" s="30"/>
     </row>
     <row r="633">
-      <c r="G633" s="25"/>
+      <c r="G633" s="30"/>
     </row>
     <row r="634">
-      <c r="G634" s="25"/>
+      <c r="G634" s="30"/>
     </row>
     <row r="635">
-      <c r="G635" s="25"/>
+      <c r="G635" s="30"/>
     </row>
     <row r="636">
-      <c r="G636" s="25"/>
+      <c r="G636" s="30"/>
     </row>
     <row r="637">
-      <c r="G637" s="25"/>
+      <c r="G637" s="30"/>
     </row>
     <row r="638">
-      <c r="G638" s="25"/>
+      <c r="G638" s="30"/>
     </row>
     <row r="639">
-      <c r="G639" s="25"/>
+      <c r="G639" s="30"/>
     </row>
     <row r="640">
-      <c r="G640" s="25"/>
+      <c r="G640" s="30"/>
     </row>
     <row r="641">
-      <c r="G641" s="25"/>
+      <c r="G641" s="30"/>
     </row>
     <row r="642">
-      <c r="G642" s="25"/>
+      <c r="G642" s="30"/>
     </row>
     <row r="643">
-      <c r="G643" s="25"/>
+      <c r="G643" s="30"/>
     </row>
     <row r="644">
-      <c r="G644" s="25"/>
+      <c r="G644" s="30"/>
     </row>
     <row r="645">
-      <c r="G645" s="25"/>
+      <c r="G645" s="30"/>
     </row>
     <row r="646">
-      <c r="G646" s="25"/>
+      <c r="G646" s="30"/>
     </row>
     <row r="647">
-      <c r="G647" s="25"/>
+      <c r="G647" s="30"/>
     </row>
     <row r="648">
-      <c r="G648" s="25"/>
+      <c r="G648" s="30"/>
     </row>
     <row r="649">
-      <c r="G649" s="25"/>
+      <c r="G649" s="30"/>
     </row>
     <row r="650">
-      <c r="G650" s="25"/>
+      <c r="G650" s="30"/>
     </row>
     <row r="651">
-      <c r="G651" s="25"/>
+      <c r="G651" s="30"/>
     </row>
     <row r="652">
-      <c r="G652" s="25"/>
+      <c r="G652" s="30"/>
     </row>
     <row r="653">
-      <c r="G653" s="25"/>
+      <c r="G653" s="30"/>
     </row>
     <row r="654">
-      <c r="G654" s="25"/>
+      <c r="G654" s="30"/>
     </row>
     <row r="655">
-      <c r="G655" s="25"/>
+      <c r="G655" s="30"/>
     </row>
     <row r="656">
-      <c r="G656" s="25"/>
+      <c r="G656" s="30"/>
     </row>
     <row r="657">
-      <c r="G657" s="25"/>
+      <c r="G657" s="30"/>
     </row>
     <row r="658">
-      <c r="G658" s="25"/>
+      <c r="G658" s="30"/>
     </row>
     <row r="659">
-      <c r="G659" s="25"/>
+      <c r="G659" s="30"/>
     </row>
     <row r="660">
-      <c r="G660" s="25"/>
+      <c r="G660" s="30"/>
     </row>
     <row r="661">
-      <c r="G661" s="25"/>
+      <c r="G661" s="30"/>
     </row>
     <row r="662">
-      <c r="G662" s="25"/>
+      <c r="G662" s="30"/>
     </row>
     <row r="663">
-      <c r="G663" s="25"/>
+      <c r="G663" s="30"/>
     </row>
     <row r="664">
-      <c r="G664" s="25"/>
+      <c r="G664" s="30"/>
     </row>
     <row r="665">
-      <c r="G665" s="25"/>
+      <c r="G665" s="30"/>
     </row>
     <row r="666">
-      <c r="G666" s="25"/>
+      <c r="G666" s="30"/>
     </row>
     <row r="667">
-      <c r="G667" s="25"/>
+      <c r="G667" s="30"/>
     </row>
     <row r="668">
-      <c r="G668" s="25"/>
+      <c r="G668" s="30"/>
     </row>
     <row r="669">
-      <c r="G669" s="25"/>
+      <c r="G669" s="30"/>
     </row>
     <row r="670">
-      <c r="G670" s="25"/>
+      <c r="G670" s="30"/>
     </row>
     <row r="671">
-      <c r="G671" s="25"/>
+      <c r="G671" s="30"/>
     </row>
     <row r="672">
-      <c r="G672" s="25"/>
+      <c r="G672" s="30"/>
     </row>
     <row r="673">
-      <c r="G673" s="25"/>
+      <c r="G673" s="30"/>
     </row>
     <row r="674">
-      <c r="G674" s="25"/>
+      <c r="G674" s="30"/>
     </row>
     <row r="675">
-      <c r="G675" s="25"/>
+      <c r="G675" s="30"/>
     </row>
     <row r="676">
-      <c r="G676" s="25"/>
+      <c r="G676" s="30"/>
     </row>
     <row r="677">
-      <c r="G677" s="25"/>
+      <c r="G677" s="30"/>
     </row>
     <row r="678">
-      <c r="G678" s="25"/>
+      <c r="G678" s="30"/>
     </row>
     <row r="679">
-      <c r="G679" s="25"/>
+      <c r="G679" s="30"/>
     </row>
     <row r="680">
-      <c r="G680" s="25"/>
+      <c r="G680" s="30"/>
     </row>
     <row r="681">
-      <c r="G681" s="25"/>
+      <c r="G681" s="30"/>
     </row>
     <row r="682">
-      <c r="G682" s="25"/>
+      <c r="G682" s="30"/>
     </row>
     <row r="683">
-      <c r="G683" s="25"/>
+      <c r="G683" s="30"/>
     </row>
     <row r="684">
-      <c r="G684" s="25"/>
+      <c r="G684" s="30"/>
     </row>
     <row r="685">
-      <c r="G685" s="25"/>
+      <c r="G685" s="30"/>
     </row>
     <row r="686">
-      <c r="G686" s="25"/>
+      <c r="G686" s="30"/>
     </row>
     <row r="687">
-      <c r="G687" s="25"/>
+      <c r="G687" s="30"/>
     </row>
     <row r="688">
-      <c r="G688" s="25"/>
+      <c r="G688" s="30"/>
     </row>
     <row r="689">
-      <c r="G689" s="25"/>
+      <c r="G689" s="30"/>
     </row>
     <row r="690">
-      <c r="G690" s="25"/>
+      <c r="G690" s="30"/>
     </row>
     <row r="691">
-      <c r="G691" s="25"/>
+      <c r="G691" s="30"/>
     </row>
     <row r="692">
-      <c r="G692" s="25"/>
+      <c r="G692" s="30"/>
     </row>
     <row r="693">
-      <c r="G693" s="25"/>
+      <c r="G693" s="30"/>
     </row>
     <row r="694">
-      <c r="G694" s="25"/>
+      <c r="G694" s="30"/>
     </row>
     <row r="695">
-      <c r="G695" s="25"/>
+      <c r="G695" s="30"/>
     </row>
     <row r="696">
-      <c r="G696" s="25"/>
+      <c r="G696" s="30"/>
     </row>
     <row r="697">
-      <c r="G697" s="25"/>
+      <c r="G697" s="30"/>
     </row>
     <row r="698">
-      <c r="G698" s="25"/>
+      <c r="G698" s="30"/>
     </row>
     <row r="699">
-      <c r="G699" s="25"/>
+      <c r="G699" s="30"/>
     </row>
     <row r="700">
-      <c r="G700" s="25"/>
+      <c r="G700" s="30"/>
     </row>
     <row r="701">
-      <c r="G701" s="25"/>
+      <c r="G701" s="30"/>
     </row>
     <row r="702">
-      <c r="G702" s="25"/>
+      <c r="G702" s="30"/>
     </row>
     <row r="703">
-      <c r="G703" s="25"/>
+      <c r="G703" s="30"/>
     </row>
     <row r="704">
-      <c r="G704" s="25"/>
+      <c r="G704" s="30"/>
     </row>
     <row r="705">
-      <c r="G705" s="25"/>
+      <c r="G705" s="30"/>
     </row>
     <row r="706">
-      <c r="G706" s="25"/>
+      <c r="G706" s="30"/>
     </row>
     <row r="707">
-      <c r="G707" s="25"/>
+      <c r="G707" s="30"/>
     </row>
     <row r="708">
-      <c r="G708" s="25"/>
+      <c r="G708" s="30"/>
     </row>
     <row r="709">
-      <c r="G709" s="25"/>
+      <c r="G709" s="30"/>
     </row>
     <row r="710">
-      <c r="G710" s="25"/>
+      <c r="G710" s="30"/>
     </row>
     <row r="711">
-      <c r="G711" s="25"/>
+      <c r="G711" s="30"/>
     </row>
     <row r="712">
-      <c r="G712" s="25"/>
+      <c r="G712" s="30"/>
     </row>
     <row r="713">
-      <c r="G713" s="25"/>
+      <c r="G713" s="30"/>
     </row>
     <row r="714">
-      <c r="G714" s="25"/>
+      <c r="G714" s="30"/>
     </row>
     <row r="715">
-      <c r="G715" s="25"/>
+      <c r="G715" s="30"/>
     </row>
     <row r="716">
-      <c r="G716" s="25"/>
+      <c r="G716" s="30"/>
     </row>
     <row r="717">
-      <c r="G717" s="25"/>
+      <c r="G717" s="30"/>
     </row>
     <row r="718">
-      <c r="G718" s="25"/>
+      <c r="G718" s="30"/>
     </row>
     <row r="719">
-      <c r="G719" s="25"/>
+      <c r="G719" s="30"/>
     </row>
     <row r="720">
-      <c r="G720" s="25"/>
+      <c r="G720" s="30"/>
     </row>
     <row r="721">
-      <c r="G721" s="25"/>
+      <c r="G721" s="30"/>
     </row>
     <row r="722">
-      <c r="G722" s="25"/>
+      <c r="G722" s="30"/>
     </row>
     <row r="723">
-      <c r="G723" s="25"/>
+      <c r="G723" s="30"/>
     </row>
     <row r="724">
-      <c r="G724" s="25"/>
+      <c r="G724" s="30"/>
     </row>
     <row r="725">
-      <c r="G725" s="25"/>
+      <c r="G725" s="30"/>
     </row>
     <row r="726">
-      <c r="G726" s="25"/>
+      <c r="G726" s="30"/>
     </row>
     <row r="727">
-      <c r="G727" s="25"/>
+      <c r="G727" s="30"/>
     </row>
     <row r="728">
-      <c r="G728" s="25"/>
+      <c r="G728" s="30"/>
     </row>
     <row r="729">
-      <c r="G729" s="25"/>
+      <c r="G729" s="30"/>
     </row>
     <row r="730">
-      <c r="G730" s="25"/>
+      <c r="G730" s="30"/>
     </row>
     <row r="731">
-      <c r="G731" s="25"/>
+      <c r="G731" s="30"/>
     </row>
     <row r="732">
-      <c r="G732" s="25"/>
+      <c r="G732" s="30"/>
     </row>
     <row r="733">
-      <c r="G733" s="25"/>
+      <c r="G733" s="30"/>
     </row>
     <row r="734">
-      <c r="G734" s="25"/>
+      <c r="G734" s="30"/>
     </row>
     <row r="735">
-      <c r="G735" s="25"/>
+      <c r="G735" s="30"/>
     </row>
     <row r="736">
-      <c r="G736" s="25"/>
+      <c r="G736" s="30"/>
     </row>
     <row r="737">
-      <c r="G737" s="25"/>
+      <c r="G737" s="30"/>
     </row>
     <row r="738">
-      <c r="G738" s="25"/>
+      <c r="G738" s="30"/>
     </row>
     <row r="739">
-      <c r="G739" s="25"/>
+      <c r="G739" s="30"/>
     </row>
     <row r="740">
-      <c r="G740" s="25"/>
+      <c r="G740" s="30"/>
     </row>
     <row r="741">
-      <c r="G741" s="25"/>
+      <c r="G741" s="30"/>
     </row>
     <row r="742">
-      <c r="G742" s="25"/>
+      <c r="G742" s="30"/>
     </row>
     <row r="743">
-      <c r="G743" s="25"/>
+      <c r="G743" s="30"/>
     </row>
     <row r="744">
-      <c r="G744" s="25"/>
+      <c r="G744" s="30"/>
     </row>
     <row r="745">
-      <c r="G745" s="25"/>
+      <c r="G745" s="30"/>
     </row>
     <row r="746">
-      <c r="G746" s="25"/>
+      <c r="G746" s="30"/>
     </row>
     <row r="747">
-      <c r="G747" s="25"/>
+      <c r="G747" s="30"/>
     </row>
     <row r="748">
-      <c r="G748" s="25"/>
+      <c r="G748" s="30"/>
     </row>
     <row r="749">
-      <c r="G749" s="25"/>
+      <c r="G749" s="30"/>
     </row>
     <row r="750">
-      <c r="G750" s="25"/>
+      <c r="G750" s="30"/>
     </row>
     <row r="751">
-      <c r="G751" s="25"/>
+      <c r="G751" s="30"/>
     </row>
     <row r="752">
-      <c r="G752" s="25"/>
+      <c r="G752" s="30"/>
     </row>
     <row r="753">
-      <c r="G753" s="25"/>
+      <c r="G753" s="30"/>
     </row>
     <row r="754">
-      <c r="G754" s="25"/>
+      <c r="G754" s="30"/>
     </row>
     <row r="755">
-      <c r="G755" s="25"/>
+      <c r="G755" s="30"/>
     </row>
     <row r="756">
-      <c r="G756" s="25"/>
+      <c r="G756" s="30"/>
     </row>
     <row r="757">
-      <c r="G757" s="25"/>
+      <c r="G757" s="30"/>
     </row>
     <row r="758">
-      <c r="G758" s="25"/>
+      <c r="G758" s="30"/>
     </row>
     <row r="759">
-      <c r="G759" s="25"/>
+      <c r="G759" s="30"/>
     </row>
     <row r="760">
-      <c r="G760" s="25"/>
+      <c r="G760" s="30"/>
     </row>
     <row r="761">
-      <c r="G761" s="25"/>
+      <c r="G761" s="30"/>
     </row>
     <row r="762">
-      <c r="G762" s="25"/>
+      <c r="G762" s="30"/>
     </row>
     <row r="763">
-      <c r="G763" s="25"/>
+      <c r="G763" s="30"/>
     </row>
     <row r="764">
-      <c r="G764" s="25"/>
+      <c r="G764" s="30"/>
     </row>
     <row r="765">
-      <c r="G765" s="25"/>
+      <c r="G765" s="30"/>
     </row>
     <row r="766">
-      <c r="G766" s="25"/>
+      <c r="G766" s="30"/>
     </row>
     <row r="767">
-      <c r="G767" s="25"/>
+      <c r="G767" s="30"/>
     </row>
     <row r="768">
-      <c r="G768" s="25"/>
+      <c r="G768" s="30"/>
     </row>
     <row r="769">
-      <c r="G769" s="25"/>
+      <c r="G769" s="30"/>
     </row>
     <row r="770">
-      <c r="G770" s="25"/>
+      <c r="G770" s="30"/>
     </row>
     <row r="771">
-      <c r="G771" s="25"/>
+      <c r="G771" s="30"/>
     </row>
     <row r="772">
-      <c r="G772" s="25"/>
+      <c r="G772" s="30"/>
     </row>
     <row r="773">
-      <c r="G773" s="25"/>
+      <c r="G773" s="30"/>
     </row>
     <row r="774">
-      <c r="G774" s="25"/>
+      <c r="G774" s="30"/>
     </row>
     <row r="775">
-      <c r="G775" s="25"/>
+      <c r="G775" s="30"/>
     </row>
     <row r="776">
-      <c r="G776" s="25"/>
+      <c r="G776" s="30"/>
     </row>
     <row r="777">
-      <c r="G777" s="25"/>
+      <c r="G777" s="30"/>
     </row>
     <row r="778">
-      <c r="G778" s="25"/>
+      <c r="G778" s="30"/>
     </row>
     <row r="779">
-      <c r="G779" s="25"/>
+      <c r="G779" s="30"/>
     </row>
     <row r="780">
-      <c r="G780" s="25"/>
+      <c r="G780" s="30"/>
     </row>
     <row r="781">
-      <c r="G781" s="25"/>
+      <c r="G781" s="30"/>
     </row>
     <row r="782">
-      <c r="G782" s="25"/>
+      <c r="G782" s="30"/>
     </row>
     <row r="783">
-      <c r="G783" s="25"/>
+      <c r="G783" s="30"/>
     </row>
     <row r="784">
-      <c r="G784" s="25"/>
+      <c r="G784" s="30"/>
     </row>
     <row r="785">
-      <c r="G785" s="25"/>
+      <c r="G785" s="30"/>
     </row>
     <row r="786">
-      <c r="G786" s="25"/>
+      <c r="G786" s="30"/>
     </row>
     <row r="787">
-      <c r="G787" s="25"/>
+      <c r="G787" s="30"/>
     </row>
     <row r="788">
-      <c r="G788" s="25"/>
+      <c r="G788" s="30"/>
     </row>
     <row r="789">
-      <c r="G789" s="25"/>
+      <c r="G789" s="30"/>
     </row>
     <row r="790">
-      <c r="G790" s="25"/>
+      <c r="G790" s="30"/>
     </row>
     <row r="791">
-      <c r="G791" s="25"/>
+      <c r="G791" s="30"/>
     </row>
     <row r="792">
-      <c r="G792" s="25"/>
+      <c r="G792" s="30"/>
     </row>
     <row r="793">
-      <c r="G793" s="25"/>
+      <c r="G793" s="30"/>
     </row>
     <row r="794">
-      <c r="G794" s="25"/>
+      <c r="G794" s="30"/>
     </row>
     <row r="795">
-      <c r="G795" s="25"/>
+      <c r="G795" s="30"/>
     </row>
     <row r="796">
-      <c r="G796" s="25"/>
+      <c r="G796" s="30"/>
     </row>
     <row r="797">
-      <c r="G797" s="25"/>
+      <c r="G797" s="30"/>
     </row>
     <row r="798">
-      <c r="G798" s="25"/>
+      <c r="G798" s="30"/>
     </row>
     <row r="799">
-      <c r="G799" s="25"/>
+      <c r="G799" s="30"/>
     </row>
     <row r="800">
-      <c r="G800" s="25"/>
+      <c r="G800" s="30"/>
     </row>
     <row r="801">
-      <c r="G801" s="25"/>
+      <c r="G801" s="30"/>
     </row>
     <row r="802">
-      <c r="G802" s="25"/>
+      <c r="G802" s="30"/>
     </row>
     <row r="803">
-      <c r="G803" s="25"/>
+      <c r="G803" s="30"/>
     </row>
     <row r="804">
-      <c r="G804" s="25"/>
+      <c r="G804" s="30"/>
     </row>
     <row r="805">
-      <c r="G805" s="25"/>
+      <c r="G805" s="30"/>
     </row>
     <row r="806">
-      <c r="G806" s="25"/>
+      <c r="G806" s="30"/>
     </row>
     <row r="807">
-      <c r="G807" s="25"/>
+      <c r="G807" s="30"/>
     </row>
     <row r="808">
-      <c r="G808" s="25"/>
+      <c r="G808" s="30"/>
     </row>
     <row r="809">
-      <c r="G809" s="25"/>
+      <c r="G809" s="30"/>
     </row>
     <row r="810">
-      <c r="G810" s="25"/>
+      <c r="G810" s="30"/>
     </row>
     <row r="811">
-      <c r="G811" s="25"/>
+      <c r="G811" s="30"/>
     </row>
     <row r="812">
-      <c r="G812" s="25"/>
+      <c r="G812" s="30"/>
     </row>
     <row r="813">
-      <c r="G813" s="25"/>
+      <c r="G813" s="30"/>
     </row>
     <row r="814">
-      <c r="G814" s="25"/>
+      <c r="G814" s="30"/>
     </row>
     <row r="815">
-      <c r="G815" s="25"/>
+      <c r="G815" s="30"/>
     </row>
     <row r="816">
-      <c r="G816" s="25"/>
+      <c r="G816" s="30"/>
     </row>
     <row r="817">
-      <c r="G817" s="25"/>
+      <c r="G817" s="30"/>
     </row>
     <row r="818">
-      <c r="G818" s="25"/>
+      <c r="G818" s="30"/>
     </row>
     <row r="819">
-      <c r="G819" s="25"/>
+      <c r="G819" s="30"/>
     </row>
     <row r="820">
-      <c r="G820" s="25"/>
+      <c r="G820" s="30"/>
     </row>
     <row r="821">
-      <c r="G821" s="25"/>
+      <c r="G821" s="30"/>
     </row>
     <row r="822">
-      <c r="G822" s="25"/>
+      <c r="G822" s="30"/>
     </row>
     <row r="823">
-      <c r="G823" s="25"/>
+      <c r="G823" s="30"/>
     </row>
     <row r="824">
-      <c r="G824" s="25"/>
+      <c r="G824" s="30"/>
     </row>
     <row r="825">
-      <c r="G825" s="25"/>
+      <c r="G825" s="30"/>
     </row>
     <row r="826">
-      <c r="G826" s="25"/>
+      <c r="G826" s="30"/>
     </row>
     <row r="827">
-      <c r="G827" s="25"/>
+      <c r="G827" s="30"/>
     </row>
     <row r="828">
-      <c r="G828" s="25"/>
+      <c r="G828" s="30"/>
     </row>
     <row r="829">
-      <c r="G829" s="25"/>
+      <c r="G829" s="30"/>
     </row>
     <row r="830">
-      <c r="G830" s="25"/>
+      <c r="G830" s="30"/>
     </row>
     <row r="831">
-      <c r="G831" s="25"/>
+      <c r="G831" s="30"/>
     </row>
     <row r="832">
-      <c r="G832" s="25"/>
+      <c r="G832" s="30"/>
     </row>
     <row r="833">
-      <c r="G833" s="25"/>
+      <c r="G833" s="30"/>
     </row>
     <row r="834">
-      <c r="G834" s="25"/>
+      <c r="G834" s="30"/>
     </row>
     <row r="835">
-      <c r="G835" s="25"/>
+      <c r="G835" s="30"/>
     </row>
     <row r="836">
-      <c r="G836" s="25"/>
+      <c r="G836" s="30"/>
     </row>
     <row r="837">
-      <c r="G837" s="25"/>
+      <c r="G837" s="30"/>
     </row>
     <row r="838">
-      <c r="G838" s="25"/>
+      <c r="G838" s="30"/>
     </row>
     <row r="839">
-      <c r="G839" s="25"/>
+      <c r="G839" s="30"/>
     </row>
     <row r="840">
-      <c r="G840" s="25"/>
+      <c r="G840" s="30"/>
     </row>
     <row r="841">
-      <c r="G841" s="25"/>
+      <c r="G841" s="30"/>
     </row>
     <row r="842">
-      <c r="G842" s="25"/>
+      <c r="G842" s="30"/>
     </row>
     <row r="843">
-      <c r="G843" s="25"/>
+      <c r="G843" s="30"/>
     </row>
     <row r="844">
-      <c r="G844" s="25"/>
+      <c r="G844" s="30"/>
     </row>
     <row r="845">
-      <c r="G845" s="25"/>
+      <c r="G845" s="30"/>
     </row>
     <row r="846">
-      <c r="G846" s="25"/>
+      <c r="G846" s="30"/>
     </row>
     <row r="847">
-      <c r="G847" s="25"/>
+      <c r="G847" s="30"/>
     </row>
     <row r="848">
-      <c r="G848" s="25"/>
+      <c r="G848" s="30"/>
     </row>
     <row r="849">
-      <c r="G849" s="25"/>
+      <c r="G849" s="30"/>
     </row>
     <row r="850">
-      <c r="G850" s="25"/>
+      <c r="G850" s="30"/>
     </row>
     <row r="851">
-      <c r="G851" s="25"/>
+      <c r="G851" s="30"/>
     </row>
     <row r="852">
-      <c r="G852" s="25"/>
+      <c r="G852" s="30"/>
     </row>
     <row r="853">
-      <c r="G853" s="25"/>
+      <c r="G853" s="30"/>
     </row>
     <row r="854">
-      <c r="G854" s="25"/>
+      <c r="G854" s="30"/>
     </row>
     <row r="855">
-      <c r="G855" s="25"/>
+      <c r="G855" s="30"/>
     </row>
     <row r="856">
-      <c r="G856" s="25"/>
+      <c r="G856" s="30"/>
     </row>
     <row r="857">
-      <c r="G857" s="25"/>
+      <c r="G857" s="30"/>
     </row>
     <row r="858">
-      <c r="G858" s="25"/>
+      <c r="G858" s="30"/>
     </row>
     <row r="859">
-      <c r="G859" s="25"/>
+      <c r="G859" s="30"/>
     </row>
     <row r="860">
-      <c r="G860" s="25"/>
+      <c r="G860" s="30"/>
     </row>
     <row r="861">
-      <c r="G861" s="25"/>
+      <c r="G861" s="30"/>
     </row>
     <row r="862">
-      <c r="G862" s="25"/>
+      <c r="G862" s="30"/>
     </row>
     <row r="863">
-      <c r="G863" s="25"/>
+      <c r="G863" s="30"/>
     </row>
     <row r="864">
-      <c r="G864" s="25"/>
+      <c r="G864" s="30"/>
     </row>
     <row r="865">
-      <c r="G865" s="25"/>
+      <c r="G865" s="30"/>
     </row>
     <row r="866">
-      <c r="G866" s="25"/>
+      <c r="G866" s="30"/>
     </row>
     <row r="867">
-      <c r="G867" s="25"/>
+      <c r="G867" s="30"/>
     </row>
     <row r="868">
-      <c r="G868" s="25"/>
+      <c r="G868" s="30"/>
     </row>
     <row r="869">
-      <c r="G869" s="25"/>
+      <c r="G869" s="30"/>
     </row>
     <row r="870">
-      <c r="G870" s="25"/>
+      <c r="G870" s="30"/>
     </row>
     <row r="871">
-      <c r="G871" s="25"/>
+      <c r="G871" s="30"/>
     </row>
     <row r="872">
-      <c r="G872" s="25"/>
+      <c r="G872" s="30"/>
     </row>
     <row r="873">
-      <c r="G873" s="25"/>
+      <c r="G873" s="30"/>
     </row>
     <row r="874">
-      <c r="G874" s="25"/>
+      <c r="G874" s="30"/>
     </row>
     <row r="875">
-      <c r="G875" s="25"/>
+      <c r="G875" s="30"/>
     </row>
     <row r="876">
-      <c r="G876" s="25"/>
+      <c r="G876" s="30"/>
     </row>
     <row r="877">
-      <c r="G877" s="25"/>
+      <c r="G877" s="30"/>
     </row>
     <row r="878">
-      <c r="G878" s="25"/>
+      <c r="G878" s="30"/>
     </row>
     <row r="879">
-      <c r="G879" s="25"/>
+      <c r="G879" s="30"/>
     </row>
     <row r="880">
-      <c r="G880" s="25"/>
+      <c r="G880" s="30"/>
     </row>
     <row r="881">
-      <c r="G881" s="25"/>
+      <c r="G881" s="30"/>
     </row>
     <row r="882">
-      <c r="G882" s="25"/>
+      <c r="G882" s="30"/>
     </row>
     <row r="883">
-      <c r="G883" s="25"/>
+      <c r="G883" s="30"/>
     </row>
     <row r="884">
-      <c r="G884" s="25"/>
+      <c r="G884" s="30"/>
     </row>
     <row r="885">
-      <c r="G885" s="25"/>
+      <c r="G885" s="30"/>
     </row>
     <row r="886">
-      <c r="G886" s="25"/>
+      <c r="G886" s="30"/>
     </row>
     <row r="887">
-      <c r="G887" s="25"/>
+      <c r="G887" s="30"/>
     </row>
     <row r="888">
-      <c r="G888" s="25"/>
+      <c r="G888" s="30"/>
     </row>
     <row r="889">
-      <c r="G889" s="25"/>
+      <c r="G889" s="30"/>
     </row>
     <row r="890">
-      <c r="G890" s="25"/>
+      <c r="G890" s="30"/>
     </row>
     <row r="891">
-      <c r="G891" s="25"/>
+      <c r="G891" s="30"/>
     </row>
     <row r="892">
-      <c r="G892" s="25"/>
+      <c r="G892" s="30"/>
     </row>
     <row r="893">
-      <c r="G893" s="25"/>
+      <c r="G893" s="30"/>
     </row>
     <row r="894">
-      <c r="G894" s="25"/>
+      <c r="G894" s="30"/>
     </row>
     <row r="895">
-      <c r="G895" s="25"/>
+      <c r="G895" s="30"/>
     </row>
     <row r="896">
-      <c r="G896" s="25"/>
+      <c r="G896" s="30"/>
     </row>
     <row r="897">
-      <c r="G897" s="25"/>
+      <c r="G897" s="30"/>
     </row>
     <row r="898">
-      <c r="G898" s="25"/>
+      <c r="G898" s="30"/>
     </row>
     <row r="899">
-      <c r="G899" s="25"/>
+      <c r="G899" s="30"/>
     </row>
     <row r="900">
-      <c r="G900" s="25"/>
+      <c r="G900" s="30"/>
     </row>
     <row r="901">
-      <c r="G901" s="25"/>
+      <c r="G901" s="30"/>
     </row>
     <row r="902">
-      <c r="G902" s="25"/>
+      <c r="G902" s="30"/>
     </row>
     <row r="903">
-      <c r="G903" s="25"/>
+      <c r="G903" s="30"/>
     </row>
     <row r="904">
-      <c r="G904" s="25"/>
+      <c r="G904" s="30"/>
     </row>
     <row r="905">
-      <c r="G905" s="25"/>
+      <c r="G905" s="30"/>
     </row>
     <row r="906">
-      <c r="G906" s="25"/>
+      <c r="G906" s="30"/>
     </row>
     <row r="907">
-      <c r="G907" s="25"/>
+      <c r="G907" s="30"/>
     </row>
     <row r="908">
-      <c r="G908" s="25"/>
+      <c r="G908" s="30"/>
     </row>
     <row r="909">
-      <c r="G909" s="25"/>
+      <c r="G909" s="30"/>
     </row>
     <row r="910">
-      <c r="G910" s="25"/>
+      <c r="G910" s="30"/>
     </row>
     <row r="911">
-      <c r="G911" s="25"/>
+      <c r="G911" s="30"/>
     </row>
     <row r="912">
-      <c r="G912" s="25"/>
+      <c r="G912" s="30"/>
     </row>
     <row r="913">
-      <c r="G913" s="25"/>
+      <c r="G913" s="30"/>
     </row>
     <row r="914">
-      <c r="G914" s="25"/>
+      <c r="G914" s="30"/>
     </row>
     <row r="915">
-      <c r="G915" s="25"/>
+      <c r="G915" s="30"/>
     </row>
     <row r="916">
-      <c r="G916" s="25"/>
+      <c r="G916" s="30"/>
     </row>
     <row r="917">
-      <c r="G917" s="25"/>
+      <c r="G917" s="30"/>
     </row>
     <row r="918">
-      <c r="G918" s="25"/>
+      <c r="G918" s="30"/>
     </row>
     <row r="919">
-      <c r="G919" s="25"/>
+      <c r="G919" s="30"/>
     </row>
     <row r="920">
-      <c r="G920" s="25"/>
+      <c r="G920" s="30"/>
     </row>
     <row r="921">
-      <c r="G921" s="25"/>
+      <c r="G921" s="30"/>
     </row>
     <row r="922">
-      <c r="G922" s="25"/>
+      <c r="G922" s="30"/>
     </row>
     <row r="923">
-      <c r="G923" s="25"/>
+      <c r="G923" s="30"/>
     </row>
     <row r="924">
-      <c r="G924" s="25"/>
+      <c r="G924" s="30"/>
     </row>
     <row r="925">
-      <c r="G925" s="25"/>
+      <c r="G925" s="30"/>
     </row>
     <row r="926">
-      <c r="G926" s="25"/>
+      <c r="G926" s="30"/>
     </row>
     <row r="927">
-      <c r="G927" s="25"/>
+      <c r="G927" s="30"/>
     </row>
     <row r="928">
-      <c r="G928" s="25"/>
+      <c r="G928" s="30"/>
     </row>
     <row r="929">
-      <c r="G929" s="25"/>
+      <c r="G929" s="30"/>
     </row>
     <row r="930">
-      <c r="G930" s="25"/>
+      <c r="G930" s="30"/>
     </row>
     <row r="931">
-      <c r="G931" s="25"/>
+      <c r="G931" s="30"/>
     </row>
     <row r="932">
-      <c r="G932" s="25"/>
+      <c r="G932" s="30"/>
     </row>
     <row r="933">
-      <c r="G933" s="25"/>
+      <c r="G933" s="30"/>
     </row>
     <row r="934">
-      <c r="G934" s="25"/>
+      <c r="G934" s="30"/>
     </row>
     <row r="935">
-      <c r="G935" s="25"/>
+      <c r="G935" s="30"/>
     </row>
     <row r="936">
-      <c r="G936" s="25"/>
+      <c r="G936" s="30"/>
     </row>
     <row r="937">
-      <c r="G937" s="25"/>
+      <c r="G937" s="30"/>
     </row>
     <row r="938">
-      <c r="G938" s="25"/>
+      <c r="G938" s="30"/>
     </row>
     <row r="939">
-      <c r="G939" s="25"/>
+      <c r="G939" s="30"/>
     </row>
     <row r="940">
-      <c r="G940" s="25"/>
+      <c r="G940" s="30"/>
     </row>
     <row r="941">
-      <c r="G941" s="25"/>
+      <c r="G941" s="30"/>
     </row>
     <row r="942">
-      <c r="G942" s="25"/>
+      <c r="G942" s="30"/>
     </row>
     <row r="943">
-      <c r="G943" s="25"/>
+      <c r="G943" s="30"/>
     </row>
     <row r="944">
-      <c r="G944" s="25"/>
+      <c r="G944" s="30"/>
     </row>
     <row r="945">
-      <c r="G945" s="25"/>
+      <c r="G945" s="30"/>
     </row>
     <row r="946">
-      <c r="G946" s="25"/>
+      <c r="G946" s="30"/>
     </row>
     <row r="947">
-      <c r="G947" s="25"/>
+      <c r="G947" s="30"/>
     </row>
     <row r="948">
-      <c r="G948" s="25"/>
+      <c r="G948" s="30"/>
     </row>
     <row r="949">
-      <c r="G949" s="25"/>
+      <c r="G949" s="30"/>
     </row>
     <row r="950">
-      <c r="G950" s="25"/>
+      <c r="G950" s="30"/>
     </row>
     <row r="951">
-      <c r="G951" s="25"/>
+      <c r="G951" s="30"/>
     </row>
     <row r="952">
-      <c r="G952" s="25"/>
+      <c r="G952" s="30"/>
     </row>
     <row r="953">
-      <c r="G953" s="25"/>
+      <c r="G953" s="30"/>
     </row>
     <row r="954">
-      <c r="G954" s="25"/>
+      <c r="G954" s="30"/>
     </row>
     <row r="955">
-      <c r="G955" s="25"/>
+      <c r="G955" s="30"/>
     </row>
     <row r="956">
-      <c r="G956" s="25"/>
+      <c r="G956" s="30"/>
     </row>
     <row r="957">
-      <c r="G957" s="25"/>
+      <c r="G957" s="30"/>
     </row>
     <row r="958">
-      <c r="G958" s="25"/>
+      <c r="G958" s="30"/>
     </row>
     <row r="959">
-      <c r="G959" s="25"/>
+      <c r="G959" s="30"/>
     </row>
     <row r="960">
-      <c r="G960" s="25"/>
+      <c r="G960" s="30"/>
     </row>
     <row r="961">
-      <c r="G961" s="25"/>
+      <c r="G961" s="30"/>
     </row>
     <row r="962">
-      <c r="G962" s="25"/>
+      <c r="G962" s="30"/>
     </row>
     <row r="963">
-      <c r="G963" s="25"/>
+      <c r="G963" s="30"/>
     </row>
     <row r="964">
-      <c r="G964" s="25"/>
+      <c r="G964" s="30"/>
     </row>
     <row r="965">
-      <c r="G965" s="25"/>
+      <c r="G965" s="30"/>
     </row>
     <row r="966">
-      <c r="G966" s="25"/>
+      <c r="G966" s="30"/>
     </row>
     <row r="967">
-      <c r="G967" s="25"/>
+      <c r="G967" s="30"/>
     </row>
     <row r="968">
-      <c r="G968" s="25"/>
+      <c r="G968" s="30"/>
     </row>
     <row r="969">
-      <c r="G969" s="25"/>
+      <c r="G969" s="30"/>
     </row>
     <row r="970">
-      <c r="G970" s="25"/>
+      <c r="G970" s="30"/>
     </row>
     <row r="971">
-      <c r="G971" s="25"/>
+      <c r="G971" s="30"/>
     </row>
     <row r="972">
-      <c r="G972" s="25"/>
+      <c r="G972" s="30"/>
     </row>
     <row r="973">
-      <c r="G973" s="25"/>
+      <c r="G973" s="30"/>
     </row>
     <row r="974">
-      <c r="G974" s="25"/>
+      <c r="G974" s="30"/>
     </row>
     <row r="975">
-      <c r="G975" s="25"/>
+      <c r="G975" s="30"/>
     </row>
     <row r="976">
-      <c r="G976" s="25"/>
+      <c r="G976" s="30"/>
     </row>
     <row r="977">
-      <c r="G977" s="25"/>
+      <c r="G977" s="30"/>
     </row>
     <row r="978">
-      <c r="G978" s="25"/>
+      <c r="G978" s="30"/>
     </row>
     <row r="979">
-      <c r="G979" s="25"/>
+      <c r="G979" s="30"/>
     </row>
     <row r="980">
-      <c r="G980" s="25"/>
+      <c r="G980" s="30"/>
     </row>
     <row r="981">
-      <c r="G981" s="25"/>
+      <c r="G981" s="30"/>
     </row>
     <row r="982">
-      <c r="G982" s="25"/>
+      <c r="G982" s="30"/>
     </row>
     <row r="983">
-      <c r="G983" s="25"/>
+      <c r="G983" s="30"/>
     </row>
     <row r="984">
-      <c r="G984" s="25"/>
+      <c r="G984" s="30"/>
     </row>
     <row r="985">
-      <c r="G985" s="25"/>
+      <c r="G985" s="30"/>
     </row>
     <row r="986">
-      <c r="G986" s="25"/>
+      <c r="G986" s="30"/>
     </row>
     <row r="987">
-      <c r="G987" s="25"/>
+      <c r="G987" s="30"/>
     </row>
     <row r="988">
-      <c r="G988" s="25"/>
+      <c r="G988" s="30"/>
     </row>
     <row r="989">
-      <c r="G989" s="25"/>
+      <c r="G989" s="30"/>
     </row>
     <row r="990">
-      <c r="G990" s="25"/>
+      <c r="G990" s="30"/>
     </row>
     <row r="991">
-      <c r="G991" s="25"/>
+      <c r="G991" s="30"/>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A25">
       <formula1>"Data,Metadata,Files"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K11 D2:D19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K11 D2:D25">
       <formula1>"Standard,Custom,Big Object (Custom),Managed Package,Standard (System/Virtual))"</formula1>
     </dataValidation>
   </dataValidations>
